--- a/web/public/forms/orig/o-dongbari-gyehoekseo.xlsx
+++ b/web/public/forms/orig/o-dongbari-gyehoekseo.xlsx
@@ -1376,7 +1376,7 @@
     <row r="1" ht="20" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">  K-건설맵  |  k-conmap.com  무료 건설 서식</t>
+          <t xml:space="preserve">  K-건설맵  |  k-conmap.com  건설 서식</t>
         </is>
       </c>
       <c r="G1" s="2" t="inlineStr">
@@ -1540,7 +1540,7 @@
     <row r="1" ht="20" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">  K-건설맵  |  k-conmap.com  무료 건설 서식</t>
+          <t xml:space="preserve">  K-건설맵  |  k-conmap.com  건설 서식</t>
         </is>
       </c>
       <c r="G1" s="2" t="inlineStr">
@@ -4155,7 +4155,7 @@
     <row r="1" ht="20" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">  K-건설맵  |  k-conmap.com  무료 건설 서식</t>
+          <t xml:space="preserve">  K-건설맵  |  k-conmap.com  건설 서식</t>
         </is>
       </c>
       <c r="G1" s="2" t="inlineStr">
@@ -4509,7 +4509,7 @@
     <row r="1" ht="20" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">  K-건설맵  |  k-conmap.com  무료 건설 서식</t>
+          <t xml:space="preserve">  K-건설맵  |  k-conmap.com  건설 서식</t>
         </is>
       </c>
       <c r="G1" s="51" t="inlineStr">
@@ -4684,7 +4684,7 @@
     <row r="1" ht="20" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">  K-건설맵  |  k-conmap.com  무료 건설 서식</t>
+          <t xml:space="preserve">  K-건설맵  |  k-conmap.com  건설 서식</t>
         </is>
       </c>
       <c r="G1" s="51" t="inlineStr">
@@ -7300,7 +7300,7 @@
     <row r="1" ht="20" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">  K-건설맵  |  k-conmap.com  무료 건설 서식</t>
+          <t xml:space="preserve">  K-건설맵  |  k-conmap.com  건설 서식</t>
         </is>
       </c>
       <c r="G1" s="51" t="inlineStr">

--- a/web/public/forms/orig/o-dongbari-gyehoekseo.xlsx
+++ b/web/public/forms/orig/o-dongbari-gyehoekseo.xlsx
@@ -10,17 +10,11 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="표지" sheetId="1" state="visible" r:id="rId1"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="본문" sheetId="2" state="visible" r:id="rId2"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="확인표" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="예시-표지" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="예시-본문" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="예시-확인표" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm.Print_Area" localSheetId="0">'표지'!$A$1:$L$12</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="1">'본문'!$A$1:$L$300</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="2">'확인표'!$A$1:$L$13</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="3">'예시-표지'!$A$1:$L$12</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="4">'예시-본문'!$A$1:$L$300</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="5">'예시-확인표'!$A$1:$L$13</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -228,7 +222,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="52">
+  <cellXfs count="51">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
@@ -377,9 +371,6 @@
     </xf>
     <xf numFmtId="0" fontId="7" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -458,311 +449,6 @@
 </file>
 
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
-<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
-  <oneCellAnchor>
-    <from>
-      <col>0</col>
-      <colOff>47625</colOff>
-      <row>21</row>
-      <rowOff>95250</rowOff>
-    </from>
-    <ext cx="2933700" cy="1828800"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="1" name="Image 1" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId1"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>6</col>
-      <colOff>47625</colOff>
-      <row>21</row>
-      <rowOff>95250</rowOff>
-    </from>
-    <ext cx="2933700" cy="1828800"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="2" name="Image 2" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId2"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>2</col>
-      <colOff>228600</colOff>
-      <row>45</row>
-      <rowOff>47625</rowOff>
-    </from>
-    <ext cx="3571875" cy="3200400"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="3" name="Image 3" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId3"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>8</col>
-      <colOff>47625</colOff>
-      <row>205</row>
-      <rowOff>28575</rowOff>
-    </from>
-    <ext cx="1924050" cy="1200150"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="4" name="Image 4" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId4"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>8</col>
-      <colOff>47625</colOff>
-      <row>216</row>
-      <rowOff>28575</rowOff>
-    </from>
-    <ext cx="1924050" cy="1200150"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="5" name="Image 5" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId5"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>6</col>
-      <colOff>47625</colOff>
-      <row>228</row>
-      <rowOff>219075</rowOff>
-    </from>
-    <ext cx="2933700" cy="1828800"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="6" name="Image 6" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId6"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>6</col>
-      <colOff>47625</colOff>
-      <row>237</row>
-      <rowOff>219075</rowOff>
-    </from>
-    <ext cx="2933700" cy="1828800"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="7" name="Image 7" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId7"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>6</col>
-      <colOff>47625</colOff>
-      <row>246</row>
-      <rowOff>219075</rowOff>
-    </from>
-    <ext cx="2933700" cy="1828800"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="8" name="Image 8" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId8"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>6</col>
-      <colOff>47625</colOff>
-      <row>255</row>
-      <rowOff>219075</rowOff>
-    </from>
-    <ext cx="2933700" cy="1828800"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="9" name="Image 9" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId9"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>6</col>
-      <colOff>47625</colOff>
-      <row>264</row>
-      <rowOff>219075</rowOff>
-    </from>
-    <ext cx="2933700" cy="1828800"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="10" name="Image 10" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId10"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>6</col>
-      <colOff>47625</colOff>
-      <row>273</row>
-      <rowOff>219075</rowOff>
-    </from>
-    <ext cx="2933700" cy="1828800"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="11" name="Image 11" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId11"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>6</col>
-      <colOff>47625</colOff>
-      <row>282</row>
-      <rowOff>219075</rowOff>
-    </from>
-    <ext cx="2933700" cy="1828800"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="12" name="Image 12" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId12"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-</wsDr>
-</file>
-
-<file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
 <wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
   <oneCellAnchor>
     <from>
@@ -1402,10 +1088,7 @@
     </row>
     <row r="5" ht="34" customHeight="1">
       <c r="A5" s="5" t="inlineStr"/>
-      <c r="C5" s="6">
-        <f>"("&amp;IF(F7="","○○",F7)&amp;" — System Support)"</f>
-        <v/>
-      </c>
+      <c r="C5" s="6" t="n"/>
       <c r="K5" s="5" t="inlineStr"/>
     </row>
     <row r="6" ht="40" customHeight="1"/>
@@ -1443,10 +1126,7 @@
     </row>
     <row r="9" ht="20" customHeight="1">
       <c r="A9" s="5" t="inlineStr"/>
-      <c r="F9" s="12">
-        <f>IF(OR(N(F8)=0,N(H8)=0),"",IF(H8&lt;F8,"⚠ 준공일이 착공일보다 빠름",H8-F8+1))</f>
-        <v/>
-      </c>
+      <c r="F9" s="12" t="n"/>
       <c r="K9" s="5" t="inlineStr"/>
     </row>
     <row r="10" ht="28" customHeight="1">
@@ -1473,6 +1153,7 @@
         </is>
       </c>
     </row>
+    <row r="13"/>
     <row r="14" ht="19.5" customHeight="1">
       <c r="A14" s="15" t="inlineStr">
         <is>
@@ -2307,10 +1988,7 @@
     </row>
     <row r="98" ht="4" customHeight="1"/>
     <row r="99" ht="22" customHeight="1">
-      <c r="A99" s="31">
-        <f>"2-1. "&amp;(IF('표지'!F7="","○○",'표지'!F7))&amp;" 시스템 동바리 설치 평면도"</f>
-        <v/>
-      </c>
+      <c r="A99" s="31" t="n"/>
     </row>
     <row r="100" ht="20" customHeight="1">
       <c r="A100" s="32" t="inlineStr">
@@ -2500,10 +2178,7 @@
     </row>
     <row r="113" ht="8" customHeight="1"/>
     <row r="114" ht="22" customHeight="1">
-      <c r="A114" s="31">
-        <f>"2-2. "&amp;(IF('표지'!F7="","○○",'표지'!F7))&amp;" 시스템 동바리 설치 단면도"</f>
-        <v/>
-      </c>
+      <c r="A114" s="31" t="n"/>
     </row>
     <row r="115" ht="20" customHeight="1">
       <c r="A115" s="32" t="inlineStr">
@@ -2693,10 +2368,7 @@
     </row>
     <row r="128" ht="8" customHeight="1"/>
     <row r="129" ht="22" customHeight="1">
-      <c r="A129" s="31">
-        <f>"2-3. "&amp;(IF('표지'!F7="","○○",'표지'!F7))&amp;" 멍에재 설치 평면도"</f>
-        <v/>
-      </c>
+      <c r="A129" s="31" t="n"/>
     </row>
     <row r="130" ht="20" customHeight="1">
       <c r="A130" s="32" t="inlineStr">
@@ -2895,10 +2567,7 @@
     </row>
     <row r="146" ht="4" customHeight="1"/>
     <row r="147" ht="22" customHeight="1">
-      <c r="A147" s="31">
-        <f>"3-1. "&amp;(IF('표지'!F7="","○○",'표지'!F7))&amp;" 시스템 비계 설치계획 도면"</f>
-        <v/>
-      </c>
+      <c r="A147" s="31" t="n"/>
     </row>
     <row r="148" ht="20" customHeight="1">
       <c r="A148" s="33" t="inlineStr">
@@ -3106,10 +2775,7 @@
     </row>
     <row r="162" ht="8" customHeight="1"/>
     <row r="163" ht="22" customHeight="1">
-      <c r="A163" s="31">
-        <f>"3-2. "&amp;(IF('표지'!F7="","○○",'표지'!F7))&amp;" 낙하물방지망 설치 도면"</f>
-        <v/>
-      </c>
+      <c r="A163" s="31" t="n"/>
     </row>
     <row r="164" ht="20" customHeight="1">
       <c r="A164" s="32" t="inlineStr">
@@ -3901,6 +3567,7 @@
         </is>
       </c>
     </row>
+    <row r="301"/>
     <row r="302" ht="34" customHeight="1">
       <c r="A302" s="15" t="inlineStr">
         <is>
@@ -4179,10 +3846,7 @@
       </c>
       <c r="B3" s="8" t="n"/>
       <c r="C3" s="8" t="n"/>
-      <c r="D3" s="39">
-        <f>IF('표지'!F7="","",'표지'!F7)</f>
-        <v/>
-      </c>
+      <c r="D3" s="39" t="n"/>
       <c r="E3" s="8" t="n"/>
       <c r="F3" s="8" t="n"/>
       <c r="G3" s="8" t="n"/>
@@ -4247,15 +3911,9 @@
       </c>
       <c r="G5" s="8" t="n"/>
       <c r="H5" s="8" t="n"/>
-      <c r="I5" s="43">
-        <f>IF(OR(N(D5)=0,N(D6)=0),"",ROUND(D5/D6,2))</f>
-        <v/>
-      </c>
+      <c r="I5" s="43" t="n"/>
       <c r="J5" s="8" t="n"/>
-      <c r="K5" s="44">
-        <f>IF(I5="","",IF(I5&lt;=3,"적합","부적합 — 붕괴방지 조치"))</f>
-        <v/>
-      </c>
+      <c r="K5" s="44" t="n"/>
       <c r="L5" s="8" t="n"/>
     </row>
     <row r="6" ht="24" customHeight="1">
@@ -4295,10 +3953,7 @@
       <c r="H7" s="8" t="n"/>
       <c r="I7" s="46" t="inlineStr"/>
       <c r="J7" s="8" t="n"/>
-      <c r="K7" s="44">
-        <f>IF(N(D7)=0,"",IF(D7&lt;=600,"적합","부적합"))</f>
-        <v/>
-      </c>
+      <c r="K7" s="44" t="n"/>
       <c r="L7" s="8" t="n"/>
     </row>
     <row r="8" ht="24" customHeight="1">
@@ -4320,10 +3975,7 @@
       <c r="H8" s="8" t="n"/>
       <c r="I8" s="46" t="inlineStr"/>
       <c r="J8" s="8" t="n"/>
-      <c r="K8" s="44">
-        <f>IF(N(D8)=0,"",IF(D8&gt;=150,"적합","부적합"))</f>
-        <v/>
-      </c>
+      <c r="K8" s="44" t="n"/>
       <c r="L8" s="8" t="n"/>
     </row>
     <row r="9" ht="24" customHeight="1">
@@ -4343,15 +3995,9 @@
       </c>
       <c r="G9" s="8" t="n"/>
       <c r="H9" s="8" t="n"/>
-      <c r="I9" s="48">
-        <f>IF(OR(N(D9)=0,N(D10)=0),"",D9-2*D10)</f>
-        <v/>
-      </c>
+      <c r="I9" s="48" t="n"/>
       <c r="J9" s="8" t="n"/>
-      <c r="K9" s="44">
-        <f>IF(I9="","",IF(I9&gt;=0,"적합","부적합"))</f>
-        <v/>
-      </c>
+      <c r="K9" s="44" t="n"/>
       <c r="L9" s="8" t="n"/>
     </row>
     <row r="10" ht="24" customHeight="1">
@@ -4380,10 +4026,7 @@
       </c>
       <c r="B11" s="8" t="n"/>
       <c r="C11" s="8" t="n"/>
-      <c r="D11" s="50">
-        <f>IF((K5&amp;K7&amp;K8&amp;K9)="","",IF(COUNTIF(K5,"부*")+COUNTIF(K7,"부*")+COUNTIF(K8,"부*")+COUNTIF(K9,"부*")=0,IF(AND(K5&lt;&gt;"",K7&lt;&gt;"",K8&lt;&gt;"",K9&lt;&gt;""),"모두 적합","적합(빈 항목 있음)"),"⚠ 부적합 항목 — 설치 계획 · 구조검토 다시 확인"))</f>
-        <v/>
-      </c>
+      <c r="D11" s="50" t="n"/>
       <c r="E11" s="8" t="n"/>
       <c r="F11" s="8" t="n"/>
       <c r="G11" s="8" t="n"/>
@@ -4422,3173 +4065,11 @@
         </is>
       </c>
     </row>
+    <row r="14"/>
     <row r="15" ht="19.5" customHeight="1">
       <c r="A15" s="15" t="inlineStr">
         <is>
           <t>노란 칸 없이 값만 적으면 비교 · 판정 · 종합이 저절로 나옵니다.</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="44">
-    <mergeCell ref="D3:G3"/>
-    <mergeCell ref="D10:E10"/>
-    <mergeCell ref="D11:L11"/>
-    <mergeCell ref="F8:H8"/>
-    <mergeCell ref="A3:C3"/>
-    <mergeCell ref="I5:J6"/>
-    <mergeCell ref="A12:C12"/>
-    <mergeCell ref="D6:E6"/>
-    <mergeCell ref="A2:L2"/>
-    <mergeCell ref="A5:C5"/>
-    <mergeCell ref="I7:J7"/>
-    <mergeCell ref="A8:C8"/>
-    <mergeCell ref="D12:F12"/>
-    <mergeCell ref="J12:L12"/>
-    <mergeCell ref="A4:C4"/>
-    <mergeCell ref="J3:L3"/>
-    <mergeCell ref="I9:J10"/>
-    <mergeCell ref="A10:C10"/>
-    <mergeCell ref="G1:L1"/>
-    <mergeCell ref="K9:L10"/>
-    <mergeCell ref="D7:E7"/>
-    <mergeCell ref="F5:H6"/>
-    <mergeCell ref="K8:L8"/>
-    <mergeCell ref="F9:H10"/>
-    <mergeCell ref="A13:L13"/>
-    <mergeCell ref="A9:C9"/>
-    <mergeCell ref="F4:H4"/>
-    <mergeCell ref="D4:E4"/>
-    <mergeCell ref="K5:L6"/>
-    <mergeCell ref="G12:I12"/>
-    <mergeCell ref="I8:J8"/>
-    <mergeCell ref="D9:E9"/>
-    <mergeCell ref="H3:I3"/>
-    <mergeCell ref="D8:E8"/>
-    <mergeCell ref="K7:L7"/>
-    <mergeCell ref="I4:J4"/>
-    <mergeCell ref="A11:C11"/>
-    <mergeCell ref="A15:L15"/>
-    <mergeCell ref="A1:F1"/>
-    <mergeCell ref="D5:E5"/>
-    <mergeCell ref="A6:C6"/>
-    <mergeCell ref="F7:H7"/>
-    <mergeCell ref="K4:L4"/>
-    <mergeCell ref="A7:C7"/>
-  </mergeCells>
-  <printOptions horizontalCentered="1"/>
-  <pageMargins left="0.6" right="0.6" top="0.6" bottom="0.6" header="0.2" footer="0.2"/>
-  <pageSetup orientation="portrait" paperSize="9" fitToHeight="1" fitToWidth="1"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <tabColor rgb="00F59E0B"/>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr fitToPage="1"/>
-  </sheetPr>
-  <dimension ref="A1:L14"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="7.6" customWidth="1" min="1" max="1"/>
-    <col width="7.6" customWidth="1" min="2" max="2"/>
-    <col width="7.6" customWidth="1" min="3" max="3"/>
-    <col width="7.6" customWidth="1" min="4" max="4"/>
-    <col width="7.6" customWidth="1" min="5" max="5"/>
-    <col width="7.6" customWidth="1" min="6" max="6"/>
-    <col width="7.6" customWidth="1" min="7" max="7"/>
-    <col width="7.6" customWidth="1" min="8" max="8"/>
-    <col width="7.6" customWidth="1" min="9" max="9"/>
-    <col width="7.6" customWidth="1" min="10" max="10"/>
-    <col width="7.6" customWidth="1" min="11" max="11"/>
-    <col width="7.6" customWidth="1" min="12" max="12"/>
-  </cols>
-  <sheetData>
-    <row r="1" ht="20" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  K-건설맵  |  k-conmap.com  건설 서식</t>
-        </is>
-      </c>
-      <c r="G1" s="51" t="inlineStr">
-        <is>
-          <t xml:space="preserve">작성 예시 (가상의 현장)  </t>
-        </is>
-      </c>
-    </row>
-    <row r="2" ht="110" customHeight="1"/>
-    <row r="3" ht="40" customHeight="1">
-      <c r="A3" s="3" t="inlineStr">
-        <is>
-          <t>가나지구 복합청사 신축공사</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" ht="70" customHeight="1">
-      <c r="A4" s="4" t="inlineStr">
-        <is>
-          <t>시 공 계 획 서</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="34" customHeight="1">
-      <c r="A5" s="5" t="inlineStr"/>
-      <c r="C5" s="6">
-        <f>"("&amp;IF(F7="","○○",F7)&amp;" — System Support)"</f>
-        <v/>
-      </c>
-      <c r="K5" s="5" t="inlineStr"/>
-    </row>
-    <row r="6" ht="40" customHeight="1"/>
-    <row r="7" ht="28" customHeight="1">
-      <c r="A7" s="5" t="inlineStr"/>
-      <c r="C7" s="7" t="inlineStr">
-        <is>
-          <t>대상 구조물 · 위치</t>
-        </is>
-      </c>
-      <c r="D7" s="8" t="n"/>
-      <c r="E7" s="8" t="n"/>
-      <c r="F7" s="9" t="inlineStr">
-        <is>
-          <t>연결통로 A</t>
-        </is>
-      </c>
-      <c r="G7" s="8" t="n"/>
-      <c r="H7" s="8" t="n"/>
-      <c r="I7" s="8" t="n"/>
-      <c r="J7" s="8" t="n"/>
-      <c r="K7" s="5" t="inlineStr"/>
-    </row>
-    <row r="8" ht="28" customHeight="1">
-      <c r="A8" s="5" t="inlineStr"/>
-      <c r="C8" s="7" t="inlineStr">
-        <is>
-          <t>공 사 기 간</t>
-        </is>
-      </c>
-      <c r="D8" s="8" t="n"/>
-      <c r="E8" s="8" t="n"/>
-      <c r="F8" s="10" t="n">
-        <v>46300</v>
-      </c>
-      <c r="G8" s="8" t="n"/>
-      <c r="H8" s="11" t="n">
-        <v>46346</v>
-      </c>
-      <c r="I8" s="8" t="n"/>
-      <c r="J8" s="8" t="n"/>
-      <c r="K8" s="5" t="inlineStr"/>
-    </row>
-    <row r="9" ht="20" customHeight="1">
-      <c r="A9" s="5" t="inlineStr"/>
-      <c r="F9" s="12">
-        <f>IF(OR(N(F8)=0,N(H8)=0),"",IF(H8&lt;F8,"⚠ 준공일이 착공일보다 빠름",H8-F8+1))</f>
-        <v/>
-      </c>
-      <c r="K9" s="5" t="inlineStr"/>
-    </row>
-    <row r="10" ht="28" customHeight="1">
-      <c r="A10" s="5" t="inlineStr"/>
-      <c r="C10" s="7" t="inlineStr">
-        <is>
-          <t>작 성 연 월</t>
-        </is>
-      </c>
-      <c r="D10" s="8" t="n"/>
-      <c r="E10" s="8" t="n"/>
-      <c r="F10" s="13" t="n">
-        <v>46266</v>
-      </c>
-      <c r="G10" s="8" t="n"/>
-      <c r="H10" s="8" t="n"/>
-      <c r="I10" s="8" t="n"/>
-      <c r="J10" s="8" t="n"/>
-      <c r="K10" s="5" t="inlineStr"/>
-    </row>
-    <row r="11" ht="150" customHeight="1"/>
-    <row r="12" ht="44" customHeight="1">
-      <c r="A12" s="14" t="inlineStr">
-        <is>
-          <t>예시건설(주)</t>
-        </is>
-      </c>
-    </row>
-    <row r="14" ht="19.5" customHeight="1">
-      <c r="A14" s="15" t="inlineStr">
-        <is>
-          <t>이 시트는 작성 예시입니다(가상의 공사 · 회사).</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="25">
-    <mergeCell ref="F10:J10"/>
-    <mergeCell ref="K9:L9"/>
-    <mergeCell ref="K5:L5"/>
-    <mergeCell ref="C5:J5"/>
-    <mergeCell ref="A3:L3"/>
-    <mergeCell ref="A12:L12"/>
-    <mergeCell ref="F7:J7"/>
-    <mergeCell ref="A7:B7"/>
-    <mergeCell ref="C8:E8"/>
-    <mergeCell ref="A14:L14"/>
-    <mergeCell ref="C7:E7"/>
-    <mergeCell ref="A4:L4"/>
-    <mergeCell ref="F8:G8"/>
-    <mergeCell ref="G1:L1"/>
-    <mergeCell ref="K8:L8"/>
-    <mergeCell ref="A5:B5"/>
-    <mergeCell ref="H8:J8"/>
-    <mergeCell ref="A8:B8"/>
-    <mergeCell ref="F9:J9"/>
-    <mergeCell ref="K7:L7"/>
-    <mergeCell ref="A1:F1"/>
-    <mergeCell ref="A10:B10"/>
-    <mergeCell ref="K10:L10"/>
-    <mergeCell ref="A9:E9"/>
-    <mergeCell ref="C10:E10"/>
-  </mergeCells>
-  <printOptions horizontalCentered="1"/>
-  <pageMargins left="0.6" right="0.6" top="0.6" bottom="0.6" header="0.2" footer="0.2"/>
-  <pageSetup orientation="portrait" paperSize="9" fitToHeight="1" fitToWidth="1"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <tabColor rgb="00F59E0B"/>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr fitToPage="1"/>
-  </sheetPr>
-  <dimension ref="A1:L302"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="7.6" customWidth="1" min="1" max="1"/>
-    <col width="7.6" customWidth="1" min="2" max="2"/>
-    <col width="7.6" customWidth="1" min="3" max="3"/>
-    <col width="7.6" customWidth="1" min="4" max="4"/>
-    <col width="7.6" customWidth="1" min="5" max="5"/>
-    <col width="7.6" customWidth="1" min="6" max="6"/>
-    <col width="7.6" customWidth="1" min="7" max="7"/>
-    <col width="7.6" customWidth="1" min="8" max="8"/>
-    <col width="7.6" customWidth="1" min="9" max="9"/>
-    <col width="7.6" customWidth="1" min="10" max="10"/>
-    <col width="7.6" customWidth="1" min="11" max="11"/>
-    <col width="7.6" customWidth="1" min="12" max="12"/>
-  </cols>
-  <sheetData>
-    <row r="1" ht="20" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  K-건설맵  |  k-conmap.com  건설 서식</t>
-        </is>
-      </c>
-      <c r="G1" s="51" t="inlineStr">
-        <is>
-          <t xml:space="preserve">작성 예시 (가상의 현장)  </t>
-        </is>
-      </c>
-    </row>
-    <row r="2" ht="16" customHeight="1"/>
-    <row r="3" ht="50" customHeight="1">
-      <c r="A3" s="16" t="inlineStr">
-        <is>
-          <t>목          차</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" ht="14" customHeight="1"/>
-    <row r="5" ht="30" customHeight="1">
-      <c r="A5" s="5" t="inlineStr"/>
-      <c r="C5" s="17" t="inlineStr">
-        <is>
-          <t>1.  System Support 개요</t>
-        </is>
-      </c>
-      <c r="K5" s="5" t="inlineStr"/>
-    </row>
-    <row r="6" ht="30" customHeight="1">
-      <c r="A6" s="5" t="inlineStr"/>
-      <c r="C6" s="17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">      1-1. 시스템 동바리의 종류     1-2. 용어의 정의</t>
-        </is>
-      </c>
-      <c r="K6" s="5" t="inlineStr"/>
-    </row>
-    <row r="7" ht="30" customHeight="1">
-      <c r="A7" s="5" t="inlineStr"/>
-      <c r="C7" s="17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">      1-3. 시스템 동바리의 특징     1-4. 시스템 동바리의 제작기준</t>
-        </is>
-      </c>
-      <c r="K7" s="5" t="inlineStr"/>
-    </row>
-    <row r="8" ht="30" customHeight="1">
-      <c r="A8" s="5" t="inlineStr"/>
-      <c r="C8" s="17" t="inlineStr">
-        <is>
-          <t>2.  System Support 도면</t>
-        </is>
-      </c>
-      <c r="K8" s="5" t="inlineStr"/>
-    </row>
-    <row r="9" ht="30" customHeight="1">
-      <c r="A9" s="5" t="inlineStr"/>
-      <c r="C9" s="17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">      2-1. 설치 평면도     2-2. 설치 단면도     2-3. 멍에재 설치 평면도</t>
-        </is>
-      </c>
-      <c r="K9" s="5" t="inlineStr"/>
-    </row>
-    <row r="10" ht="30" customHeight="1">
-      <c r="A10" s="5" t="inlineStr"/>
-      <c r="C10" s="17" t="inlineStr">
-        <is>
-          <t>3.  시스템 비계 · 낙하물방지망 설치계획</t>
-        </is>
-      </c>
-      <c r="K10" s="5" t="inlineStr"/>
-    </row>
-    <row r="11" ht="30" customHeight="1">
-      <c r="A11" s="5" t="inlineStr"/>
-      <c r="C11" s="17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">      3-1. 시스템 비계 설치계획 도면     3-2. 낙하물방지망 설치 도면</t>
-        </is>
-      </c>
-      <c r="K11" s="5" t="inlineStr"/>
-    </row>
-    <row r="12" ht="30" customHeight="1">
-      <c r="A12" s="5" t="inlineStr"/>
-      <c r="C12" s="17" t="inlineStr">
-        <is>
-          <t>4.  System Support 시공계획</t>
-        </is>
-      </c>
-      <c r="K12" s="5" t="inlineStr"/>
-    </row>
-    <row r="13" ht="30" customHeight="1">
-      <c r="A13" s="5" t="inlineStr"/>
-      <c r="C13" s="17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">      4-1. System Support 순서도     4-2. 조립 및 해체     ※ 설치 조건 확인표</t>
-        </is>
-      </c>
-      <c r="K13" s="5" t="inlineStr"/>
-    </row>
-    <row r="14" ht="4" customHeight="1"/>
-    <row r="15" ht="30" customHeight="1">
-      <c r="A15" s="18" t="inlineStr">
-        <is>
-          <t>1.  System Support 개요</t>
-        </is>
-      </c>
-    </row>
-    <row r="16" ht="4" customHeight="1"/>
-    <row r="17" ht="3" customHeight="1"/>
-    <row r="18" ht="22" customHeight="1">
-      <c r="A18" s="19" t="inlineStr">
-        <is>
-          <t>1-1. 시스템 동바리의 종류</t>
-        </is>
-      </c>
-    </row>
-    <row r="19" ht="52.5" customHeight="1">
-      <c r="A19" s="20" t="inlineStr">
-        <is>
-          <t>시스템 동바리는 크게 두 종류로 나뉜다. 하나는 수평 서포트와 수직 서포트의 역할을 함께 하는 보 형태의 트러스재이고, 다른 하나는 수직하중과 횡력을 함께 부담하는 지주 형태의 시스템 동바리이다.</t>
-        </is>
-      </c>
-    </row>
-    <row r="20" ht="20" customHeight="1"/>
-    <row r="21" ht="20" customHeight="1"/>
-    <row r="22" ht="20" customHeight="1"/>
-    <row r="23" ht="20" customHeight="1"/>
-    <row r="24" ht="20" customHeight="1"/>
-    <row r="25" ht="20" customHeight="1"/>
-    <row r="26" ht="20" customHeight="1"/>
-    <row r="27" ht="20" customHeight="1"/>
-    <row r="28" ht="20" customHeight="1"/>
-    <row r="29" ht="20" customHeight="1"/>
-    <row r="30" ht="20" customHeight="1"/>
-    <row r="31" ht="20" customHeight="1"/>
-    <row r="32" ht="20" customHeight="1">
-      <c r="A32" s="21" t="inlineStr">
-        <is>
-          <t>(1) 지주 형태식 시스템 동바리</t>
-        </is>
-      </c>
-      <c r="G32" s="21" t="inlineStr">
-        <is>
-          <t>(2) 보 형태식 시스템 동바리</t>
-        </is>
-      </c>
-    </row>
-    <row r="33" ht="44" customHeight="1">
-      <c r="A33" s="22" t="inlineStr">
-        <is>
-          <t>거푸집 동바리 · 가설 작업대 · 승강 계단 등 여러 용도로 쓸 수 있으며, 특히 설치 높이가 높고 슬래브 두께가 큰 구조물의 동바리로 많이 쓴다.</t>
-        </is>
-      </c>
-      <c r="G33" s="22" t="inlineStr">
-        <is>
-          <t>기존 파이프 서포트의 약점인 설치 뒤 작업공간 부족과 시공기간 · 소요인력 · 안전성을 개선한 형태이다.</t>
-        </is>
-      </c>
-    </row>
-    <row r="34" ht="3" customHeight="1"/>
-    <row r="35" ht="22" customHeight="1">
-      <c r="A35" s="19" t="inlineStr">
-        <is>
-          <t>1-2. 용어의 정의</t>
-        </is>
-      </c>
-    </row>
-    <row r="36" ht="46.85" customHeight="1">
-      <c r="A36" s="23" t="inlineStr">
-        <is>
-          <t>(1)</t>
-        </is>
-      </c>
-      <c r="B36" s="22" t="inlineStr">
-        <is>
-          <t>«시스템 동바리» — 각목 · 파이프 서포트 · 강관틀(B/T) 지주 등은 작용하중이 크거나 층고가 높은 곳에 설치하기 어렵고 위험하므로, 지주를 부품화 · 조립화하여 설치가 간편하고 하중을 안전하게 전달할 수 있게 만든 가설 구조물</t>
-        </is>
-      </c>
-    </row>
-    <row r="37" ht="18.95" customHeight="1">
-      <c r="A37" s="23" t="inlineStr">
-        <is>
-          <t>(2)</t>
-        </is>
-      </c>
-      <c r="B37" s="22" t="inlineStr">
-        <is>
-          <t>«수직재» — 거푸집의 상부하중을 하부로 전달하는 주요 부재</t>
-        </is>
-      </c>
-    </row>
-    <row r="38" ht="18.95" customHeight="1">
-      <c r="A38" s="23" t="inlineStr">
-        <is>
-          <t>(3)</t>
-        </is>
-      </c>
-      <c r="B38" s="22" t="inlineStr">
-        <is>
-          <t>«수평재» — 수직재의 좌굴을 막기 위해 수평으로 연결하는 부재</t>
-        </is>
-      </c>
-    </row>
-    <row r="39" ht="18.95" customHeight="1">
-      <c r="A39" s="23" t="inlineStr">
-        <is>
-          <t>(4)</t>
-        </is>
-      </c>
-      <c r="B39" s="22" t="inlineStr">
-        <is>
-          <t>«링» — 수직재에 용접으로 고정하여 수평재를 수직재와 연결 · 고정할 수 있게 만든 부재</t>
-        </is>
-      </c>
-    </row>
-    <row r="40" ht="18.95" customHeight="1">
-      <c r="A40" s="23" t="inlineStr">
-        <is>
-          <t>(5)</t>
-        </is>
-      </c>
-      <c r="B40" s="22" t="inlineStr">
-        <is>
-          <t>«연결핀» — 수직재와 수직재, 링과 가새 또는 수평재와 링을 연결 · 고정하는 부재</t>
-        </is>
-      </c>
-    </row>
-    <row r="41" ht="18.95" customHeight="1">
-      <c r="A41" s="23" t="inlineStr">
-        <is>
-          <t>(6)</t>
-        </is>
-      </c>
-      <c r="B41" s="22" t="inlineStr">
-        <is>
-          <t>«U헤드 잭» — 수직재 상부에 설치하여 멍에재를 연결하는 조절형 받침대</t>
-        </is>
-      </c>
-    </row>
-    <row r="42" ht="18.95" customHeight="1">
-      <c r="A42" s="23" t="inlineStr">
-        <is>
-          <t>(7)</t>
-        </is>
-      </c>
-      <c r="B42" s="22" t="inlineStr">
-        <is>
-          <t>«잭 베이스» — 하부에 설치하여 수직재의 수평 · 수직을 유지하는 조절형 받침대</t>
-        </is>
-      </c>
-    </row>
-    <row r="43" ht="18.95" customHeight="1">
-      <c r="A43" s="23" t="inlineStr">
-        <is>
-          <t>(8)</t>
-        </is>
-      </c>
-      <c r="B43" s="22" t="inlineStr">
-        <is>
-          <t>«장선» — 거푸집 널 하부에 고정하여 상부하중을 멍에에 전달하는 부재</t>
-        </is>
-      </c>
-    </row>
-    <row r="44" ht="32.90000000000001" customHeight="1">
-      <c r="A44" s="23" t="inlineStr">
-        <is>
-          <t>(9)</t>
-        </is>
-      </c>
-      <c r="B44" s="22" t="inlineStr">
-        <is>
-          <t>«멍에» — 장선을 지지하고 상부하중을 하부구조에 전달하기 위해 장선과 직각 방향으로 설치하는 부재</t>
-        </is>
-      </c>
-    </row>
-    <row r="45" ht="18.95" customHeight="1">
-      <c r="A45" s="23" t="inlineStr">
-        <is>
-          <t>(10)</t>
-        </is>
-      </c>
-      <c r="B45" s="22" t="inlineStr">
-        <is>
-          <t>«가새» — 횡력에 견딜 수 있도록 수평재와 수평재, 수직재와 수직재를 연결하여 고정하는 부재</t>
-        </is>
-      </c>
-    </row>
-    <row r="46" ht="20" customHeight="1"/>
-    <row r="47" ht="20" customHeight="1"/>
-    <row r="48" ht="20" customHeight="1"/>
-    <row r="49" ht="20" customHeight="1"/>
-    <row r="50" ht="20" customHeight="1"/>
-    <row r="51" ht="20" customHeight="1"/>
-    <row r="52" ht="20" customHeight="1"/>
-    <row r="53" ht="20" customHeight="1"/>
-    <row r="54" ht="20" customHeight="1"/>
-    <row r="55" ht="20" customHeight="1"/>
-    <row r="56" ht="20" customHeight="1"/>
-    <row r="57" ht="20" customHeight="1"/>
-    <row r="58" ht="20" customHeight="1"/>
-    <row r="59" ht="18" customHeight="1">
-      <c r="A59" s="24" t="inlineStr">
-        <is>
-          <t>[ 시스템 동바리 부재 명칭 ]</t>
-        </is>
-      </c>
-    </row>
-    <row r="60" ht="3" customHeight="1"/>
-    <row r="61" ht="22" customHeight="1">
-      <c r="A61" s="19" t="inlineStr">
-        <is>
-          <t>1-3. 시스템 동바리의 특징</t>
-        </is>
-      </c>
-    </row>
-    <row r="62" ht="21" customHeight="1">
-      <c r="A62" s="5" t="inlineStr"/>
-      <c r="B62" s="25" t="inlineStr">
-        <is>
-          <t>가. 파이프 서포트의 장 · 단점</t>
-        </is>
-      </c>
-    </row>
-    <row r="63" ht="19.725" customHeight="1">
-      <c r="A63" s="26" t="inlineStr">
-        <is>
-          <t>(1)</t>
-        </is>
-      </c>
-      <c r="C63" s="27" t="inlineStr">
-        <is>
-          <t>거푸집 설치 때 장선 · 멍에와 동바리의 고정이 불편하다.</t>
-        </is>
-      </c>
-    </row>
-    <row r="64" ht="19.725" customHeight="1">
-      <c r="A64" s="26" t="inlineStr">
-        <is>
-          <t>(2)</t>
-        </is>
-      </c>
-      <c r="C64" s="27" t="inlineStr">
-        <is>
-          <t>정확하게 수직으로 설치하기 어려워 좌굴 위험이 크다.</t>
-        </is>
-      </c>
-    </row>
-    <row r="65" ht="19.725" customHeight="1">
-      <c r="A65" s="26" t="inlineStr">
-        <is>
-          <t>(3)</t>
-        </is>
-      </c>
-      <c r="C65" s="27" t="inlineStr">
-        <is>
-          <t>설계에 따른 동바리 설치 간격을 현장 여건상 정확히 지키기 어렵다.</t>
-        </is>
-      </c>
-    </row>
-    <row r="66" ht="34.45" customHeight="1">
-      <c r="A66" s="26" t="inlineStr">
-        <is>
-          <t>(4)</t>
-        </is>
-      </c>
-      <c r="C66" s="27" t="inlineStr">
-        <is>
-          <t>수평 보강 연결재를 정확한 간격으로 설치하기 어렵고, 조임철물의 조임 토크가 일정하지 않아 풀릴 위험이 있으며 설치 · 해체가 불편하다.</t>
-        </is>
-      </c>
-    </row>
-    <row r="67" ht="19.725" customHeight="1">
-      <c r="A67" s="26" t="inlineStr">
-        <is>
-          <t>(5)</t>
-        </is>
-      </c>
-      <c r="C67" s="27" t="inlineStr">
-        <is>
-          <t>높거나 반복되는 대형 구조물에 적용하기 곤란하다.</t>
-        </is>
-      </c>
-    </row>
-    <row r="68" ht="19.725" customHeight="1">
-      <c r="A68" s="26" t="inlineStr">
-        <is>
-          <t>(6)</t>
-        </is>
-      </c>
-      <c r="C68" s="27" t="inlineStr">
-        <is>
-          <t>재사용 때 지지핀을 잃어버려 일반 철근 등을 쓰면 성능을 확보하기 어렵다.</t>
-        </is>
-      </c>
-    </row>
-    <row r="69" ht="19.725" customHeight="1">
-      <c r="A69" s="26" t="inlineStr">
-        <is>
-          <t>(7)</t>
-        </is>
-      </c>
-      <c r="C69" s="27" t="inlineStr">
-        <is>
-          <t>설치 비용이 시스템 동바리보다 싸다.</t>
-        </is>
-      </c>
-    </row>
-    <row r="70" ht="19.725" customHeight="1">
-      <c r="A70" s="26" t="inlineStr">
-        <is>
-          <t>(8)</t>
-        </is>
-      </c>
-      <c r="C70" s="27" t="inlineStr">
-        <is>
-          <t>소규모 구조물에 유리하다.</t>
-        </is>
-      </c>
-    </row>
-    <row r="71" ht="21" customHeight="1">
-      <c r="A71" s="5" t="inlineStr"/>
-      <c r="B71" s="25" t="inlineStr">
-        <is>
-          <t>나. 시스템 동바리의 장 · 단점</t>
-        </is>
-      </c>
-    </row>
-    <row r="72" ht="19.725" customHeight="1">
-      <c r="A72" s="26" t="inlineStr">
-        <is>
-          <t>(1)</t>
-        </is>
-      </c>
-      <c r="C72" s="27" t="inlineStr">
-        <is>
-          <t>상 · 하부 스크루 잭과 거푸집의 연결이 확실하다.</t>
-        </is>
-      </c>
-    </row>
-    <row r="73" ht="19.725" customHeight="1">
-      <c r="A73" s="26" t="inlineStr">
-        <is>
-          <t>(2)</t>
-        </is>
-      </c>
-      <c r="C73" s="27" t="inlineStr">
-        <is>
-          <t>부재가 단순하여 시공이 쉽다.</t>
-        </is>
-      </c>
-    </row>
-    <row r="74" ht="19.725" customHeight="1">
-      <c r="A74" s="26" t="inlineStr">
-        <is>
-          <t>(3)</t>
-        </is>
-      </c>
-      <c r="C74" s="27" t="inlineStr">
-        <is>
-          <t>수직 · 수평재를 확실히 체결하여 좌굴을 막을 수 있다.</t>
-        </is>
-      </c>
-    </row>
-    <row r="75" ht="19.725" customHeight="1">
-      <c r="A75" s="26" t="inlineStr">
-        <is>
-          <t>(4)</t>
-        </is>
-      </c>
-      <c r="C75" s="27" t="inlineStr">
-        <is>
-          <t>동바리(수직재) 간격을 설치계획대로 정확히 하여 자재 과다 투입을 막을 수 있다.</t>
-        </is>
-      </c>
-    </row>
-    <row r="76" ht="19.725" customHeight="1">
-      <c r="A76" s="26" t="inlineStr">
-        <is>
-          <t>(5)</t>
-        </is>
-      </c>
-      <c r="C76" s="27" t="inlineStr">
-        <is>
-          <t>대형 구조물에 쓸 때 수평재 간격을 쉽게 조절하여 수직재 허용내력을 높일 수 있다.</t>
-        </is>
-      </c>
-    </row>
-    <row r="77" ht="3" customHeight="1"/>
-    <row r="78" ht="22" customHeight="1">
-      <c r="A78" s="19" t="inlineStr">
-        <is>
-          <t>1-4. 시스템 동바리의 제작기준</t>
-        </is>
-      </c>
-    </row>
-    <row r="79" ht="37" customHeight="1">
-      <c r="A79" s="20" t="inlineStr">
-        <is>
-          <t>시스템 동바리 각 부재의 재료는 아래 표의 기준에 맞거나 그 이상의 기계적 성질을 가져야 한다.</t>
-        </is>
-      </c>
-    </row>
-    <row r="80" ht="24" customHeight="1">
-      <c r="A80" s="28" t="inlineStr">
-        <is>
-          <t>구성 부분</t>
-        </is>
-      </c>
-      <c r="B80" s="8" t="n"/>
-      <c r="C80" s="8" t="n"/>
-      <c r="D80" s="28" t="inlineStr">
-        <is>
-          <t>규    격</t>
-        </is>
-      </c>
-      <c r="E80" s="8" t="n"/>
-      <c r="F80" s="8" t="n"/>
-      <c r="G80" s="8" t="n"/>
-      <c r="H80" s="8" t="n"/>
-      <c r="I80" s="28" t="inlineStr">
-        <is>
-          <t>비    고</t>
-        </is>
-      </c>
-      <c r="J80" s="8" t="n"/>
-      <c r="K80" s="8" t="n"/>
-      <c r="L80" s="8" t="n"/>
-    </row>
-    <row r="81" ht="33" customHeight="1">
-      <c r="A81" s="29" t="inlineStr">
-        <is>
-          <t>수직재</t>
-        </is>
-      </c>
-      <c r="B81" s="8" t="n"/>
-      <c r="C81" s="8" t="n"/>
-      <c r="D81" s="29" t="inlineStr">
-        <is>
-          <t>KS D 3566(일반구조용 탄소강관)에 정한 SPS500 의 규격</t>
-        </is>
-      </c>
-      <c r="E81" s="8" t="n"/>
-      <c r="F81" s="8" t="n"/>
-      <c r="G81" s="8" t="n"/>
-      <c r="H81" s="8" t="n"/>
-      <c r="I81" s="29" t="inlineStr"/>
-      <c r="J81" s="8" t="n"/>
-      <c r="K81" s="8" t="n"/>
-      <c r="L81" s="8" t="n"/>
-    </row>
-    <row r="82" ht="33" customHeight="1">
-      <c r="A82" s="29" t="inlineStr">
-        <is>
-          <t>수평재 및 가새</t>
-        </is>
-      </c>
-      <c r="B82" s="8" t="n"/>
-      <c r="C82" s="8" t="n"/>
-      <c r="D82" s="29" t="inlineStr">
-        <is>
-          <t>KS D 3566(일반구조용 탄소강관)에 정한 SPS400 의 규격</t>
-        </is>
-      </c>
-      <c r="E82" s="8" t="n"/>
-      <c r="F82" s="8" t="n"/>
-      <c r="G82" s="8" t="n"/>
-      <c r="H82" s="8" t="n"/>
-      <c r="I82" s="29" t="inlineStr"/>
-      <c r="J82" s="8" t="n"/>
-      <c r="K82" s="8" t="n"/>
-      <c r="L82" s="8" t="n"/>
-    </row>
-    <row r="83" ht="46.5" customHeight="1">
-      <c r="A83" s="29" t="inlineStr">
-        <is>
-          <t>링</t>
-        </is>
-      </c>
-      <c r="B83" s="8" t="n"/>
-      <c r="C83" s="8" t="n"/>
-      <c r="D83" s="29" t="inlineStr">
-        <is>
-          <t>KS D 3503(일반구조용 압연강재)에 정한 SS400 의 규격 또는 KS D 4101(탄소강 주강품)에 정한 SC410 의 규격</t>
-        </is>
-      </c>
-      <c r="E83" s="8" t="n"/>
-      <c r="F83" s="8" t="n"/>
-      <c r="G83" s="8" t="n"/>
-      <c r="H83" s="8" t="n"/>
-      <c r="I83" s="29" t="inlineStr"/>
-      <c r="J83" s="8" t="n"/>
-      <c r="K83" s="8" t="n"/>
-      <c r="L83" s="8" t="n"/>
-    </row>
-    <row r="84" ht="46.5" customHeight="1">
-      <c r="A84" s="29" t="inlineStr">
-        <is>
-          <t>연결핀</t>
-        </is>
-      </c>
-      <c r="B84" s="8" t="n"/>
-      <c r="C84" s="8" t="n"/>
-      <c r="D84" s="29" t="inlineStr">
-        <is>
-          <t>KS D 3503 에 정한 SS330 의 규격, KS D 3566 에 정한 SPS400 의 규격</t>
-        </is>
-      </c>
-      <c r="E84" s="8" t="n"/>
-      <c r="F84" s="8" t="n"/>
-      <c r="G84" s="8" t="n"/>
-      <c r="H84" s="8" t="n"/>
-      <c r="I84" s="29" t="inlineStr">
-        <is>
-          <t>옛 노동부 고시 방호장치 성능검정 규정(가설기자재)의 «강관 틀비계용 주틀의 연결핀» 규격에 준함</t>
-        </is>
-      </c>
-      <c r="J84" s="8" t="n"/>
-      <c r="K84" s="8" t="n"/>
-      <c r="L84" s="8" t="n"/>
-    </row>
-    <row r="85" ht="33" customHeight="1">
-      <c r="A85" s="29" t="inlineStr">
-        <is>
-          <t>조절형 받침철물(잭 베이스 · U헤드 잭)</t>
-        </is>
-      </c>
-      <c r="B85" s="8" t="n"/>
-      <c r="C85" s="8" t="n"/>
-      <c r="D85" s="29" t="inlineStr">
-        <is>
-          <t>KS D 3503(일반구조용 압연강재)에 정한 SS400 의 규격</t>
-        </is>
-      </c>
-      <c r="E85" s="8" t="n"/>
-      <c r="F85" s="8" t="n"/>
-      <c r="G85" s="8" t="n"/>
-      <c r="H85" s="8" t="n"/>
-      <c r="I85" s="29" t="inlineStr"/>
-      <c r="J85" s="8" t="n"/>
-      <c r="K85" s="8" t="n"/>
-      <c r="L85" s="8" t="n"/>
-    </row>
-    <row r="86" ht="41.975" customHeight="1">
-      <c r="A86" s="30" t="inlineStr">
-        <is>
-          <t>※ 원본(옛 KOSHA CODE) 표 그대로입니다. 2016년 KS 개정으로 강재 기호가 바뀌었습니다(예 : KS D 3503 SS400 → SS275, SS330 → SS235, KS D 3566 강관 기호도 변경). 현행 KS 기호와 제조사의 안전인증 · 성능 자료를 확인하세요. KOSHA CODE(현 KOSHA GUIDE)는 법적 강제사항이 아닌 권장 기술지침입니다.</t>
-        </is>
-      </c>
-    </row>
-    <row r="87" ht="19.725" customHeight="1">
-      <c r="A87" s="26" t="inlineStr">
-        <is>
-          <t>(1)</t>
-        </is>
-      </c>
-      <c r="B87" s="27" t="inlineStr">
-        <is>
-          <t>모든 강재는 표면에 갈라짐 · 찌그러짐 등 손상이 있는 것을 쓰지 않는다.</t>
-        </is>
-      </c>
-    </row>
-    <row r="88" ht="19.725" customHeight="1">
-      <c r="A88" s="26" t="inlineStr">
-        <is>
-          <t>(2)</t>
-        </is>
-      </c>
-      <c r="B88" s="27" t="inlineStr">
-        <is>
-          <t>강재는 절단면이 수직이 되도록 정확하게 잘라 휨 응력이 생기지 않게 한다.</t>
-        </is>
-      </c>
-    </row>
-    <row r="89" ht="19.725" customHeight="1">
-      <c r="A89" s="26" t="inlineStr">
-        <is>
-          <t>(3)</t>
-        </is>
-      </c>
-      <c r="B89" s="27" t="inlineStr">
-        <is>
-          <t>프레스 및 가공기계로 가공 부위에 찌그러짐 등 변형이 없게 한다.</t>
-        </is>
-      </c>
-    </row>
-    <row r="90" ht="19.725" customHeight="1">
-      <c r="A90" s="26" t="inlineStr">
-        <is>
-          <t>(4)</t>
-        </is>
-      </c>
-      <c r="B90" s="27" t="inlineStr">
-        <is>
-          <t>부재를 구부릴 때는 절곡기계를 쓰며 구부린 곳에 터짐 · 균열이 없게 한다.</t>
-        </is>
-      </c>
-    </row>
-    <row r="91" ht="19.725" customHeight="1">
-      <c r="A91" s="26" t="inlineStr">
-        <is>
-          <t>(5)</t>
-        </is>
-      </c>
-      <c r="B91" s="27" t="inlineStr">
-        <is>
-          <t>용접재료는 KS 규격에 맞는 것을 쓴다.</t>
-        </is>
-      </c>
-    </row>
-    <row r="92" ht="19.725" customHeight="1">
-      <c r="A92" s="26" t="inlineStr">
-        <is>
-          <t>(6)</t>
-        </is>
-      </c>
-      <c r="B92" s="27" t="inlineStr">
-        <is>
-          <t>용접부와 가공 · 절단면의 날카로운 부분, 변형된 부분은 매끄럽게 처리한다.</t>
-        </is>
-      </c>
-    </row>
-    <row r="93" ht="19.725" customHeight="1">
-      <c r="A93" s="26" t="inlineStr">
-        <is>
-          <t>(7)</t>
-        </is>
-      </c>
-      <c r="B93" s="27" t="inlineStr">
-        <is>
-          <t>모든 용접은 CO₂ 아크 용접으로 하며 용접열에 의한 뒤틀림 등 변형이 없게 한다.</t>
-        </is>
-      </c>
-    </row>
-    <row r="94" ht="19.725" customHeight="1">
-      <c r="A94" s="26" t="inlineStr">
-        <is>
-          <t>(8)</t>
-        </is>
-      </c>
-      <c r="B94" s="27" t="inlineStr">
-        <is>
-          <t>용접 비드가 고르게 생기게 한다.</t>
-        </is>
-      </c>
-    </row>
-    <row r="95" ht="19.725" customHeight="1">
-      <c r="A95" s="26" t="inlineStr">
-        <is>
-          <t>(9)</t>
-        </is>
-      </c>
-      <c r="B95" s="27" t="inlineStr">
-        <is>
-          <t>부재의 도금은 KS D 8308(용융 아연 도금)에 정한 2종 HDZ45 규격에 준한다.</t>
-        </is>
-      </c>
-    </row>
-    <row r="96" ht="4" customHeight="1"/>
-    <row r="97" ht="30" customHeight="1">
-      <c r="A97" s="18" t="inlineStr">
-        <is>
-          <t>2.  System Support 도면</t>
-        </is>
-      </c>
-    </row>
-    <row r="98" ht="4" customHeight="1"/>
-    <row r="99" ht="22" customHeight="1">
-      <c r="A99" s="31">
-        <f>"2-1. "&amp;(IF('예시-표지'!F7="","○○",'예시-표지'!F7))&amp;" 시스템 동바리 설치 평면도"</f>
-        <v/>
-      </c>
-    </row>
-    <row r="100" ht="20" customHeight="1">
-      <c r="A100" s="32" t="inlineStr">
-        <is>
-          <t>(시스템 동바리 설치 평면도 · 상세도를 붙이는 곳 — 구조검토서에 따른 수직재 간격 · 수평재 단수 표시)</t>
-        </is>
-      </c>
-      <c r="B100" s="8" t="n"/>
-      <c r="C100" s="8" t="n"/>
-      <c r="D100" s="8" t="n"/>
-      <c r="E100" s="8" t="n"/>
-      <c r="F100" s="8" t="n"/>
-      <c r="G100" s="8" t="n"/>
-      <c r="H100" s="8" t="n"/>
-      <c r="I100" s="8" t="n"/>
-      <c r="J100" s="8" t="n"/>
-      <c r="K100" s="8" t="n"/>
-      <c r="L100" s="8" t="n"/>
-    </row>
-    <row r="101" ht="20" customHeight="1">
-      <c r="A101" s="8" t="n"/>
-      <c r="B101" s="8" t="n"/>
-      <c r="C101" s="8" t="n"/>
-      <c r="D101" s="8" t="n"/>
-      <c r="E101" s="8" t="n"/>
-      <c r="F101" s="8" t="n"/>
-      <c r="G101" s="8" t="n"/>
-      <c r="H101" s="8" t="n"/>
-      <c r="I101" s="8" t="n"/>
-      <c r="J101" s="8" t="n"/>
-      <c r="K101" s="8" t="n"/>
-      <c r="L101" s="8" t="n"/>
-    </row>
-    <row r="102" ht="20" customHeight="1">
-      <c r="A102" s="8" t="n"/>
-      <c r="B102" s="8" t="n"/>
-      <c r="C102" s="8" t="n"/>
-      <c r="D102" s="8" t="n"/>
-      <c r="E102" s="8" t="n"/>
-      <c r="F102" s="8" t="n"/>
-      <c r="G102" s="8" t="n"/>
-      <c r="H102" s="8" t="n"/>
-      <c r="I102" s="8" t="n"/>
-      <c r="J102" s="8" t="n"/>
-      <c r="K102" s="8" t="n"/>
-      <c r="L102" s="8" t="n"/>
-    </row>
-    <row r="103" ht="20" customHeight="1">
-      <c r="A103" s="8" t="n"/>
-      <c r="B103" s="8" t="n"/>
-      <c r="C103" s="8" t="n"/>
-      <c r="D103" s="8" t="n"/>
-      <c r="E103" s="8" t="n"/>
-      <c r="F103" s="8" t="n"/>
-      <c r="G103" s="8" t="n"/>
-      <c r="H103" s="8" t="n"/>
-      <c r="I103" s="8" t="n"/>
-      <c r="J103" s="8" t="n"/>
-      <c r="K103" s="8" t="n"/>
-      <c r="L103" s="8" t="n"/>
-    </row>
-    <row r="104" ht="20" customHeight="1">
-      <c r="A104" s="8" t="n"/>
-      <c r="B104" s="8" t="n"/>
-      <c r="C104" s="8" t="n"/>
-      <c r="D104" s="8" t="n"/>
-      <c r="E104" s="8" t="n"/>
-      <c r="F104" s="8" t="n"/>
-      <c r="G104" s="8" t="n"/>
-      <c r="H104" s="8" t="n"/>
-      <c r="I104" s="8" t="n"/>
-      <c r="J104" s="8" t="n"/>
-      <c r="K104" s="8" t="n"/>
-      <c r="L104" s="8" t="n"/>
-    </row>
-    <row r="105" ht="20" customHeight="1">
-      <c r="A105" s="8" t="n"/>
-      <c r="B105" s="8" t="n"/>
-      <c r="C105" s="8" t="n"/>
-      <c r="D105" s="8" t="n"/>
-      <c r="E105" s="8" t="n"/>
-      <c r="F105" s="8" t="n"/>
-      <c r="G105" s="8" t="n"/>
-      <c r="H105" s="8" t="n"/>
-      <c r="I105" s="8" t="n"/>
-      <c r="J105" s="8" t="n"/>
-      <c r="K105" s="8" t="n"/>
-      <c r="L105" s="8" t="n"/>
-    </row>
-    <row r="106" ht="20" customHeight="1">
-      <c r="A106" s="8" t="n"/>
-      <c r="B106" s="8" t="n"/>
-      <c r="C106" s="8" t="n"/>
-      <c r="D106" s="8" t="n"/>
-      <c r="E106" s="8" t="n"/>
-      <c r="F106" s="8" t="n"/>
-      <c r="G106" s="8" t="n"/>
-      <c r="H106" s="8" t="n"/>
-      <c r="I106" s="8" t="n"/>
-      <c r="J106" s="8" t="n"/>
-      <c r="K106" s="8" t="n"/>
-      <c r="L106" s="8" t="n"/>
-    </row>
-    <row r="107" ht="20" customHeight="1">
-      <c r="A107" s="8" t="n"/>
-      <c r="B107" s="8" t="n"/>
-      <c r="C107" s="8" t="n"/>
-      <c r="D107" s="8" t="n"/>
-      <c r="E107" s="8" t="n"/>
-      <c r="F107" s="8" t="n"/>
-      <c r="G107" s="8" t="n"/>
-      <c r="H107" s="8" t="n"/>
-      <c r="I107" s="8" t="n"/>
-      <c r="J107" s="8" t="n"/>
-      <c r="K107" s="8" t="n"/>
-      <c r="L107" s="8" t="n"/>
-    </row>
-    <row r="108" ht="20" customHeight="1">
-      <c r="A108" s="8" t="n"/>
-      <c r="B108" s="8" t="n"/>
-      <c r="C108" s="8" t="n"/>
-      <c r="D108" s="8" t="n"/>
-      <c r="E108" s="8" t="n"/>
-      <c r="F108" s="8" t="n"/>
-      <c r="G108" s="8" t="n"/>
-      <c r="H108" s="8" t="n"/>
-      <c r="I108" s="8" t="n"/>
-      <c r="J108" s="8" t="n"/>
-      <c r="K108" s="8" t="n"/>
-      <c r="L108" s="8" t="n"/>
-    </row>
-    <row r="109" ht="20" customHeight="1">
-      <c r="A109" s="8" t="n"/>
-      <c r="B109" s="8" t="n"/>
-      <c r="C109" s="8" t="n"/>
-      <c r="D109" s="8" t="n"/>
-      <c r="E109" s="8" t="n"/>
-      <c r="F109" s="8" t="n"/>
-      <c r="G109" s="8" t="n"/>
-      <c r="H109" s="8" t="n"/>
-      <c r="I109" s="8" t="n"/>
-      <c r="J109" s="8" t="n"/>
-      <c r="K109" s="8" t="n"/>
-      <c r="L109" s="8" t="n"/>
-    </row>
-    <row r="110" ht="20" customHeight="1">
-      <c r="A110" s="8" t="n"/>
-      <c r="B110" s="8" t="n"/>
-      <c r="C110" s="8" t="n"/>
-      <c r="D110" s="8" t="n"/>
-      <c r="E110" s="8" t="n"/>
-      <c r="F110" s="8" t="n"/>
-      <c r="G110" s="8" t="n"/>
-      <c r="H110" s="8" t="n"/>
-      <c r="I110" s="8" t="n"/>
-      <c r="J110" s="8" t="n"/>
-      <c r="K110" s="8" t="n"/>
-      <c r="L110" s="8" t="n"/>
-    </row>
-    <row r="111" ht="20" customHeight="1">
-      <c r="A111" s="8" t="n"/>
-      <c r="B111" s="8" t="n"/>
-      <c r="C111" s="8" t="n"/>
-      <c r="D111" s="8" t="n"/>
-      <c r="E111" s="8" t="n"/>
-      <c r="F111" s="8" t="n"/>
-      <c r="G111" s="8" t="n"/>
-      <c r="H111" s="8" t="n"/>
-      <c r="I111" s="8" t="n"/>
-      <c r="J111" s="8" t="n"/>
-      <c r="K111" s="8" t="n"/>
-      <c r="L111" s="8" t="n"/>
-    </row>
-    <row r="112" ht="20" customHeight="1">
-      <c r="A112" s="8" t="n"/>
-      <c r="B112" s="8" t="n"/>
-      <c r="C112" s="8" t="n"/>
-      <c r="D112" s="8" t="n"/>
-      <c r="E112" s="8" t="n"/>
-      <c r="F112" s="8" t="n"/>
-      <c r="G112" s="8" t="n"/>
-      <c r="H112" s="8" t="n"/>
-      <c r="I112" s="8" t="n"/>
-      <c r="J112" s="8" t="n"/>
-      <c r="K112" s="8" t="n"/>
-      <c r="L112" s="8" t="n"/>
-    </row>
-    <row r="113" ht="8" customHeight="1"/>
-    <row r="114" ht="22" customHeight="1">
-      <c r="A114" s="31">
-        <f>"2-2. "&amp;(IF('예시-표지'!F7="","○○",'예시-표지'!F7))&amp;" 시스템 동바리 설치 단면도"</f>
-        <v/>
-      </c>
-    </row>
-    <row r="115" ht="20" customHeight="1">
-      <c r="A115" s="32" t="inlineStr">
-        <is>
-          <t>(시스템 동바리 설치 단면도 · 상세도를 붙이는 곳 — 구조검토서에 따른 수직재 간격 · 수평재 단수 표시)</t>
-        </is>
-      </c>
-      <c r="B115" s="8" t="n"/>
-      <c r="C115" s="8" t="n"/>
-      <c r="D115" s="8" t="n"/>
-      <c r="E115" s="8" t="n"/>
-      <c r="F115" s="8" t="n"/>
-      <c r="G115" s="8" t="n"/>
-      <c r="H115" s="8" t="n"/>
-      <c r="I115" s="8" t="n"/>
-      <c r="J115" s="8" t="n"/>
-      <c r="K115" s="8" t="n"/>
-      <c r="L115" s="8" t="n"/>
-    </row>
-    <row r="116" ht="20" customHeight="1">
-      <c r="A116" s="8" t="n"/>
-      <c r="B116" s="8" t="n"/>
-      <c r="C116" s="8" t="n"/>
-      <c r="D116" s="8" t="n"/>
-      <c r="E116" s="8" t="n"/>
-      <c r="F116" s="8" t="n"/>
-      <c r="G116" s="8" t="n"/>
-      <c r="H116" s="8" t="n"/>
-      <c r="I116" s="8" t="n"/>
-      <c r="J116" s="8" t="n"/>
-      <c r="K116" s="8" t="n"/>
-      <c r="L116" s="8" t="n"/>
-    </row>
-    <row r="117" ht="20" customHeight="1">
-      <c r="A117" s="8" t="n"/>
-      <c r="B117" s="8" t="n"/>
-      <c r="C117" s="8" t="n"/>
-      <c r="D117" s="8" t="n"/>
-      <c r="E117" s="8" t="n"/>
-      <c r="F117" s="8" t="n"/>
-      <c r="G117" s="8" t="n"/>
-      <c r="H117" s="8" t="n"/>
-      <c r="I117" s="8" t="n"/>
-      <c r="J117" s="8" t="n"/>
-      <c r="K117" s="8" t="n"/>
-      <c r="L117" s="8" t="n"/>
-    </row>
-    <row r="118" ht="20" customHeight="1">
-      <c r="A118" s="8" t="n"/>
-      <c r="B118" s="8" t="n"/>
-      <c r="C118" s="8" t="n"/>
-      <c r="D118" s="8" t="n"/>
-      <c r="E118" s="8" t="n"/>
-      <c r="F118" s="8" t="n"/>
-      <c r="G118" s="8" t="n"/>
-      <c r="H118" s="8" t="n"/>
-      <c r="I118" s="8" t="n"/>
-      <c r="J118" s="8" t="n"/>
-      <c r="K118" s="8" t="n"/>
-      <c r="L118" s="8" t="n"/>
-    </row>
-    <row r="119" ht="20" customHeight="1">
-      <c r="A119" s="8" t="n"/>
-      <c r="B119" s="8" t="n"/>
-      <c r="C119" s="8" t="n"/>
-      <c r="D119" s="8" t="n"/>
-      <c r="E119" s="8" t="n"/>
-      <c r="F119" s="8" t="n"/>
-      <c r="G119" s="8" t="n"/>
-      <c r="H119" s="8" t="n"/>
-      <c r="I119" s="8" t="n"/>
-      <c r="J119" s="8" t="n"/>
-      <c r="K119" s="8" t="n"/>
-      <c r="L119" s="8" t="n"/>
-    </row>
-    <row r="120" ht="20" customHeight="1">
-      <c r="A120" s="8" t="n"/>
-      <c r="B120" s="8" t="n"/>
-      <c r="C120" s="8" t="n"/>
-      <c r="D120" s="8" t="n"/>
-      <c r="E120" s="8" t="n"/>
-      <c r="F120" s="8" t="n"/>
-      <c r="G120" s="8" t="n"/>
-      <c r="H120" s="8" t="n"/>
-      <c r="I120" s="8" t="n"/>
-      <c r="J120" s="8" t="n"/>
-      <c r="K120" s="8" t="n"/>
-      <c r="L120" s="8" t="n"/>
-    </row>
-    <row r="121" ht="20" customHeight="1">
-      <c r="A121" s="8" t="n"/>
-      <c r="B121" s="8" t="n"/>
-      <c r="C121" s="8" t="n"/>
-      <c r="D121" s="8" t="n"/>
-      <c r="E121" s="8" t="n"/>
-      <c r="F121" s="8" t="n"/>
-      <c r="G121" s="8" t="n"/>
-      <c r="H121" s="8" t="n"/>
-      <c r="I121" s="8" t="n"/>
-      <c r="J121" s="8" t="n"/>
-      <c r="K121" s="8" t="n"/>
-      <c r="L121" s="8" t="n"/>
-    </row>
-    <row r="122" ht="20" customHeight="1">
-      <c r="A122" s="8" t="n"/>
-      <c r="B122" s="8" t="n"/>
-      <c r="C122" s="8" t="n"/>
-      <c r="D122" s="8" t="n"/>
-      <c r="E122" s="8" t="n"/>
-      <c r="F122" s="8" t="n"/>
-      <c r="G122" s="8" t="n"/>
-      <c r="H122" s="8" t="n"/>
-      <c r="I122" s="8" t="n"/>
-      <c r="J122" s="8" t="n"/>
-      <c r="K122" s="8" t="n"/>
-      <c r="L122" s="8" t="n"/>
-    </row>
-    <row r="123" ht="20" customHeight="1">
-      <c r="A123" s="8" t="n"/>
-      <c r="B123" s="8" t="n"/>
-      <c r="C123" s="8" t="n"/>
-      <c r="D123" s="8" t="n"/>
-      <c r="E123" s="8" t="n"/>
-      <c r="F123" s="8" t="n"/>
-      <c r="G123" s="8" t="n"/>
-      <c r="H123" s="8" t="n"/>
-      <c r="I123" s="8" t="n"/>
-      <c r="J123" s="8" t="n"/>
-      <c r="K123" s="8" t="n"/>
-      <c r="L123" s="8" t="n"/>
-    </row>
-    <row r="124" ht="20" customHeight="1">
-      <c r="A124" s="8" t="n"/>
-      <c r="B124" s="8" t="n"/>
-      <c r="C124" s="8" t="n"/>
-      <c r="D124" s="8" t="n"/>
-      <c r="E124" s="8" t="n"/>
-      <c r="F124" s="8" t="n"/>
-      <c r="G124" s="8" t="n"/>
-      <c r="H124" s="8" t="n"/>
-      <c r="I124" s="8" t="n"/>
-      <c r="J124" s="8" t="n"/>
-      <c r="K124" s="8" t="n"/>
-      <c r="L124" s="8" t="n"/>
-    </row>
-    <row r="125" ht="20" customHeight="1">
-      <c r="A125" s="8" t="n"/>
-      <c r="B125" s="8" t="n"/>
-      <c r="C125" s="8" t="n"/>
-      <c r="D125" s="8" t="n"/>
-      <c r="E125" s="8" t="n"/>
-      <c r="F125" s="8" t="n"/>
-      <c r="G125" s="8" t="n"/>
-      <c r="H125" s="8" t="n"/>
-      <c r="I125" s="8" t="n"/>
-      <c r="J125" s="8" t="n"/>
-      <c r="K125" s="8" t="n"/>
-      <c r="L125" s="8" t="n"/>
-    </row>
-    <row r="126" ht="20" customHeight="1">
-      <c r="A126" s="8" t="n"/>
-      <c r="B126" s="8" t="n"/>
-      <c r="C126" s="8" t="n"/>
-      <c r="D126" s="8" t="n"/>
-      <c r="E126" s="8" t="n"/>
-      <c r="F126" s="8" t="n"/>
-      <c r="G126" s="8" t="n"/>
-      <c r="H126" s="8" t="n"/>
-      <c r="I126" s="8" t="n"/>
-      <c r="J126" s="8" t="n"/>
-      <c r="K126" s="8" t="n"/>
-      <c r="L126" s="8" t="n"/>
-    </row>
-    <row r="127" ht="20" customHeight="1">
-      <c r="A127" s="8" t="n"/>
-      <c r="B127" s="8" t="n"/>
-      <c r="C127" s="8" t="n"/>
-      <c r="D127" s="8" t="n"/>
-      <c r="E127" s="8" t="n"/>
-      <c r="F127" s="8" t="n"/>
-      <c r="G127" s="8" t="n"/>
-      <c r="H127" s="8" t="n"/>
-      <c r="I127" s="8" t="n"/>
-      <c r="J127" s="8" t="n"/>
-      <c r="K127" s="8" t="n"/>
-      <c r="L127" s="8" t="n"/>
-    </row>
-    <row r="128" ht="8" customHeight="1"/>
-    <row r="129" ht="22" customHeight="1">
-      <c r="A129" s="31">
-        <f>"2-3. "&amp;(IF('예시-표지'!F7="","○○",'예시-표지'!F7))&amp;" 멍에재 설치 평면도"</f>
-        <v/>
-      </c>
-    </row>
-    <row r="130" ht="20" customHeight="1">
-      <c r="A130" s="32" t="inlineStr">
-        <is>
-          <t>(멍에재 설치 평면도 · 상세도를 붙이는 곳 — 구조검토서에 따른 수직재 간격 · 수평재 단수 표시)</t>
-        </is>
-      </c>
-      <c r="B130" s="8" t="n"/>
-      <c r="C130" s="8" t="n"/>
-      <c r="D130" s="8" t="n"/>
-      <c r="E130" s="8" t="n"/>
-      <c r="F130" s="8" t="n"/>
-      <c r="G130" s="8" t="n"/>
-      <c r="H130" s="8" t="n"/>
-      <c r="I130" s="8" t="n"/>
-      <c r="J130" s="8" t="n"/>
-      <c r="K130" s="8" t="n"/>
-      <c r="L130" s="8" t="n"/>
-    </row>
-    <row r="131" ht="20" customHeight="1">
-      <c r="A131" s="8" t="n"/>
-      <c r="B131" s="8" t="n"/>
-      <c r="C131" s="8" t="n"/>
-      <c r="D131" s="8" t="n"/>
-      <c r="E131" s="8" t="n"/>
-      <c r="F131" s="8" t="n"/>
-      <c r="G131" s="8" t="n"/>
-      <c r="H131" s="8" t="n"/>
-      <c r="I131" s="8" t="n"/>
-      <c r="J131" s="8" t="n"/>
-      <c r="K131" s="8" t="n"/>
-      <c r="L131" s="8" t="n"/>
-    </row>
-    <row r="132" ht="20" customHeight="1">
-      <c r="A132" s="8" t="n"/>
-      <c r="B132" s="8" t="n"/>
-      <c r="C132" s="8" t="n"/>
-      <c r="D132" s="8" t="n"/>
-      <c r="E132" s="8" t="n"/>
-      <c r="F132" s="8" t="n"/>
-      <c r="G132" s="8" t="n"/>
-      <c r="H132" s="8" t="n"/>
-      <c r="I132" s="8" t="n"/>
-      <c r="J132" s="8" t="n"/>
-      <c r="K132" s="8" t="n"/>
-      <c r="L132" s="8" t="n"/>
-    </row>
-    <row r="133" ht="20" customHeight="1">
-      <c r="A133" s="8" t="n"/>
-      <c r="B133" s="8" t="n"/>
-      <c r="C133" s="8" t="n"/>
-      <c r="D133" s="8" t="n"/>
-      <c r="E133" s="8" t="n"/>
-      <c r="F133" s="8" t="n"/>
-      <c r="G133" s="8" t="n"/>
-      <c r="H133" s="8" t="n"/>
-      <c r="I133" s="8" t="n"/>
-      <c r="J133" s="8" t="n"/>
-      <c r="K133" s="8" t="n"/>
-      <c r="L133" s="8" t="n"/>
-    </row>
-    <row r="134" ht="20" customHeight="1">
-      <c r="A134" s="8" t="n"/>
-      <c r="B134" s="8" t="n"/>
-      <c r="C134" s="8" t="n"/>
-      <c r="D134" s="8" t="n"/>
-      <c r="E134" s="8" t="n"/>
-      <c r="F134" s="8" t="n"/>
-      <c r="G134" s="8" t="n"/>
-      <c r="H134" s="8" t="n"/>
-      <c r="I134" s="8" t="n"/>
-      <c r="J134" s="8" t="n"/>
-      <c r="K134" s="8" t="n"/>
-      <c r="L134" s="8" t="n"/>
-    </row>
-    <row r="135" ht="20" customHeight="1">
-      <c r="A135" s="8" t="n"/>
-      <c r="B135" s="8" t="n"/>
-      <c r="C135" s="8" t="n"/>
-      <c r="D135" s="8" t="n"/>
-      <c r="E135" s="8" t="n"/>
-      <c r="F135" s="8" t="n"/>
-      <c r="G135" s="8" t="n"/>
-      <c r="H135" s="8" t="n"/>
-      <c r="I135" s="8" t="n"/>
-      <c r="J135" s="8" t="n"/>
-      <c r="K135" s="8" t="n"/>
-      <c r="L135" s="8" t="n"/>
-    </row>
-    <row r="136" ht="20" customHeight="1">
-      <c r="A136" s="8" t="n"/>
-      <c r="B136" s="8" t="n"/>
-      <c r="C136" s="8" t="n"/>
-      <c r="D136" s="8" t="n"/>
-      <c r="E136" s="8" t="n"/>
-      <c r="F136" s="8" t="n"/>
-      <c r="G136" s="8" t="n"/>
-      <c r="H136" s="8" t="n"/>
-      <c r="I136" s="8" t="n"/>
-      <c r="J136" s="8" t="n"/>
-      <c r="K136" s="8" t="n"/>
-      <c r="L136" s="8" t="n"/>
-    </row>
-    <row r="137" ht="20" customHeight="1">
-      <c r="A137" s="8" t="n"/>
-      <c r="B137" s="8" t="n"/>
-      <c r="C137" s="8" t="n"/>
-      <c r="D137" s="8" t="n"/>
-      <c r="E137" s="8" t="n"/>
-      <c r="F137" s="8" t="n"/>
-      <c r="G137" s="8" t="n"/>
-      <c r="H137" s="8" t="n"/>
-      <c r="I137" s="8" t="n"/>
-      <c r="J137" s="8" t="n"/>
-      <c r="K137" s="8" t="n"/>
-      <c r="L137" s="8" t="n"/>
-    </row>
-    <row r="138" ht="20" customHeight="1">
-      <c r="A138" s="8" t="n"/>
-      <c r="B138" s="8" t="n"/>
-      <c r="C138" s="8" t="n"/>
-      <c r="D138" s="8" t="n"/>
-      <c r="E138" s="8" t="n"/>
-      <c r="F138" s="8" t="n"/>
-      <c r="G138" s="8" t="n"/>
-      <c r="H138" s="8" t="n"/>
-      <c r="I138" s="8" t="n"/>
-      <c r="J138" s="8" t="n"/>
-      <c r="K138" s="8" t="n"/>
-      <c r="L138" s="8" t="n"/>
-    </row>
-    <row r="139" ht="20" customHeight="1">
-      <c r="A139" s="8" t="n"/>
-      <c r="B139" s="8" t="n"/>
-      <c r="C139" s="8" t="n"/>
-      <c r="D139" s="8" t="n"/>
-      <c r="E139" s="8" t="n"/>
-      <c r="F139" s="8" t="n"/>
-      <c r="G139" s="8" t="n"/>
-      <c r="H139" s="8" t="n"/>
-      <c r="I139" s="8" t="n"/>
-      <c r="J139" s="8" t="n"/>
-      <c r="K139" s="8" t="n"/>
-      <c r="L139" s="8" t="n"/>
-    </row>
-    <row r="140" ht="20" customHeight="1">
-      <c r="A140" s="8" t="n"/>
-      <c r="B140" s="8" t="n"/>
-      <c r="C140" s="8" t="n"/>
-      <c r="D140" s="8" t="n"/>
-      <c r="E140" s="8" t="n"/>
-      <c r="F140" s="8" t="n"/>
-      <c r="G140" s="8" t="n"/>
-      <c r="H140" s="8" t="n"/>
-      <c r="I140" s="8" t="n"/>
-      <c r="J140" s="8" t="n"/>
-      <c r="K140" s="8" t="n"/>
-      <c r="L140" s="8" t="n"/>
-    </row>
-    <row r="141" ht="20" customHeight="1">
-      <c r="A141" s="8" t="n"/>
-      <c r="B141" s="8" t="n"/>
-      <c r="C141" s="8" t="n"/>
-      <c r="D141" s="8" t="n"/>
-      <c r="E141" s="8" t="n"/>
-      <c r="F141" s="8" t="n"/>
-      <c r="G141" s="8" t="n"/>
-      <c r="H141" s="8" t="n"/>
-      <c r="I141" s="8" t="n"/>
-      <c r="J141" s="8" t="n"/>
-      <c r="K141" s="8" t="n"/>
-      <c r="L141" s="8" t="n"/>
-    </row>
-    <row r="142" ht="20" customHeight="1">
-      <c r="A142" s="8" t="n"/>
-      <c r="B142" s="8" t="n"/>
-      <c r="C142" s="8" t="n"/>
-      <c r="D142" s="8" t="n"/>
-      <c r="E142" s="8" t="n"/>
-      <c r="F142" s="8" t="n"/>
-      <c r="G142" s="8" t="n"/>
-      <c r="H142" s="8" t="n"/>
-      <c r="I142" s="8" t="n"/>
-      <c r="J142" s="8" t="n"/>
-      <c r="K142" s="8" t="n"/>
-      <c r="L142" s="8" t="n"/>
-    </row>
-    <row r="143" ht="8" customHeight="1"/>
-    <row r="144" ht="4" customHeight="1"/>
-    <row r="145" ht="30" customHeight="1">
-      <c r="A145" s="18" t="inlineStr">
-        <is>
-          <t>3.  시스템 비계 · 낙하물방지망 설치계획</t>
-        </is>
-      </c>
-    </row>
-    <row r="146" ht="4" customHeight="1"/>
-    <row r="147" ht="22" customHeight="1">
-      <c r="A147" s="31">
-        <f>"3-1. "&amp;(IF('예시-표지'!F7="","○○",'예시-표지'!F7))&amp;" 시스템 비계 설치계획 도면"</f>
-        <v/>
-      </c>
-    </row>
-    <row r="148" ht="20" customHeight="1">
-      <c r="A148" s="33" t="inlineStr">
-        <is>
-          <t>(1단 벽체 작업 — 비계 설치도)</t>
-        </is>
-      </c>
-      <c r="B148" s="8" t="n"/>
-      <c r="C148" s="8" t="n"/>
-      <c r="D148" s="8" t="n"/>
-      <c r="E148" s="8" t="n"/>
-      <c r="F148" s="8" t="n"/>
-      <c r="G148" s="33" t="inlineStr">
-        <is>
-          <t>(2단 벽체 · 슬래브 작업 — 비계 설치도)</t>
-        </is>
-      </c>
-      <c r="H148" s="8" t="n"/>
-      <c r="I148" s="8" t="n"/>
-      <c r="J148" s="8" t="n"/>
-      <c r="K148" s="8" t="n"/>
-      <c r="L148" s="8" t="n"/>
-    </row>
-    <row r="149" ht="20" customHeight="1">
-      <c r="A149" s="8" t="n"/>
-      <c r="B149" s="8" t="n"/>
-      <c r="C149" s="8" t="n"/>
-      <c r="D149" s="8" t="n"/>
-      <c r="E149" s="8" t="n"/>
-      <c r="F149" s="8" t="n"/>
-      <c r="G149" s="8" t="n"/>
-      <c r="H149" s="8" t="n"/>
-      <c r="I149" s="8" t="n"/>
-      <c r="J149" s="8" t="n"/>
-      <c r="K149" s="8" t="n"/>
-      <c r="L149" s="8" t="n"/>
-    </row>
-    <row r="150" ht="20" customHeight="1">
-      <c r="A150" s="8" t="n"/>
-      <c r="B150" s="8" t="n"/>
-      <c r="C150" s="8" t="n"/>
-      <c r="D150" s="8" t="n"/>
-      <c r="E150" s="8" t="n"/>
-      <c r="F150" s="8" t="n"/>
-      <c r="G150" s="8" t="n"/>
-      <c r="H150" s="8" t="n"/>
-      <c r="I150" s="8" t="n"/>
-      <c r="J150" s="8" t="n"/>
-      <c r="K150" s="8" t="n"/>
-      <c r="L150" s="8" t="n"/>
-    </row>
-    <row r="151" ht="20" customHeight="1">
-      <c r="A151" s="8" t="n"/>
-      <c r="B151" s="8" t="n"/>
-      <c r="C151" s="8" t="n"/>
-      <c r="D151" s="8" t="n"/>
-      <c r="E151" s="8" t="n"/>
-      <c r="F151" s="8" t="n"/>
-      <c r="G151" s="8" t="n"/>
-      <c r="H151" s="8" t="n"/>
-      <c r="I151" s="8" t="n"/>
-      <c r="J151" s="8" t="n"/>
-      <c r="K151" s="8" t="n"/>
-      <c r="L151" s="8" t="n"/>
-    </row>
-    <row r="152" ht="20" customHeight="1">
-      <c r="A152" s="8" t="n"/>
-      <c r="B152" s="8" t="n"/>
-      <c r="C152" s="8" t="n"/>
-      <c r="D152" s="8" t="n"/>
-      <c r="E152" s="8" t="n"/>
-      <c r="F152" s="8" t="n"/>
-      <c r="G152" s="8" t="n"/>
-      <c r="H152" s="8" t="n"/>
-      <c r="I152" s="8" t="n"/>
-      <c r="J152" s="8" t="n"/>
-      <c r="K152" s="8" t="n"/>
-      <c r="L152" s="8" t="n"/>
-    </row>
-    <row r="153" ht="20" customHeight="1">
-      <c r="A153" s="8" t="n"/>
-      <c r="B153" s="8" t="n"/>
-      <c r="C153" s="8" t="n"/>
-      <c r="D153" s="8" t="n"/>
-      <c r="E153" s="8" t="n"/>
-      <c r="F153" s="8" t="n"/>
-      <c r="G153" s="8" t="n"/>
-      <c r="H153" s="8" t="n"/>
-      <c r="I153" s="8" t="n"/>
-      <c r="J153" s="8" t="n"/>
-      <c r="K153" s="8" t="n"/>
-      <c r="L153" s="8" t="n"/>
-    </row>
-    <row r="154" ht="20" customHeight="1">
-      <c r="A154" s="8" t="n"/>
-      <c r="B154" s="8" t="n"/>
-      <c r="C154" s="8" t="n"/>
-      <c r="D154" s="8" t="n"/>
-      <c r="E154" s="8" t="n"/>
-      <c r="F154" s="8" t="n"/>
-      <c r="G154" s="8" t="n"/>
-      <c r="H154" s="8" t="n"/>
-      <c r="I154" s="8" t="n"/>
-      <c r="J154" s="8" t="n"/>
-      <c r="K154" s="8" t="n"/>
-      <c r="L154" s="8" t="n"/>
-    </row>
-    <row r="155" ht="20" customHeight="1">
-      <c r="A155" s="8" t="n"/>
-      <c r="B155" s="8" t="n"/>
-      <c r="C155" s="8" t="n"/>
-      <c r="D155" s="8" t="n"/>
-      <c r="E155" s="8" t="n"/>
-      <c r="F155" s="8" t="n"/>
-      <c r="G155" s="8" t="n"/>
-      <c r="H155" s="8" t="n"/>
-      <c r="I155" s="8" t="n"/>
-      <c r="J155" s="8" t="n"/>
-      <c r="K155" s="8" t="n"/>
-      <c r="L155" s="8" t="n"/>
-    </row>
-    <row r="156" ht="20" customHeight="1">
-      <c r="A156" s="8" t="n"/>
-      <c r="B156" s="8" t="n"/>
-      <c r="C156" s="8" t="n"/>
-      <c r="D156" s="8" t="n"/>
-      <c r="E156" s="8" t="n"/>
-      <c r="F156" s="8" t="n"/>
-      <c r="G156" s="8" t="n"/>
-      <c r="H156" s="8" t="n"/>
-      <c r="I156" s="8" t="n"/>
-      <c r="J156" s="8" t="n"/>
-      <c r="K156" s="8" t="n"/>
-      <c r="L156" s="8" t="n"/>
-    </row>
-    <row r="157" ht="20" customHeight="1">
-      <c r="A157" s="8" t="n"/>
-      <c r="B157" s="8" t="n"/>
-      <c r="C157" s="8" t="n"/>
-      <c r="D157" s="8" t="n"/>
-      <c r="E157" s="8" t="n"/>
-      <c r="F157" s="8" t="n"/>
-      <c r="G157" s="8" t="n"/>
-      <c r="H157" s="8" t="n"/>
-      <c r="I157" s="8" t="n"/>
-      <c r="J157" s="8" t="n"/>
-      <c r="K157" s="8" t="n"/>
-      <c r="L157" s="8" t="n"/>
-    </row>
-    <row r="158" ht="20" customHeight="1">
-      <c r="A158" s="8" t="n"/>
-      <c r="B158" s="8" t="n"/>
-      <c r="C158" s="8" t="n"/>
-      <c r="D158" s="8" t="n"/>
-      <c r="E158" s="8" t="n"/>
-      <c r="F158" s="8" t="n"/>
-      <c r="G158" s="8" t="n"/>
-      <c r="H158" s="8" t="n"/>
-      <c r="I158" s="8" t="n"/>
-      <c r="J158" s="8" t="n"/>
-      <c r="K158" s="8" t="n"/>
-      <c r="L158" s="8" t="n"/>
-    </row>
-    <row r="159" ht="20" customHeight="1">
-      <c r="A159" s="8" t="n"/>
-      <c r="B159" s="8" t="n"/>
-      <c r="C159" s="8" t="n"/>
-      <c r="D159" s="8" t="n"/>
-      <c r="E159" s="8" t="n"/>
-      <c r="F159" s="8" t="n"/>
-      <c r="G159" s="8" t="n"/>
-      <c r="H159" s="8" t="n"/>
-      <c r="I159" s="8" t="n"/>
-      <c r="J159" s="8" t="n"/>
-      <c r="K159" s="8" t="n"/>
-      <c r="L159" s="8" t="n"/>
-    </row>
-    <row r="160" ht="20" customHeight="1">
-      <c r="A160" s="8" t="n"/>
-      <c r="B160" s="8" t="n"/>
-      <c r="C160" s="8" t="n"/>
-      <c r="D160" s="8" t="n"/>
-      <c r="E160" s="8" t="n"/>
-      <c r="F160" s="8" t="n"/>
-      <c r="G160" s="8" t="n"/>
-      <c r="H160" s="8" t="n"/>
-      <c r="I160" s="8" t="n"/>
-      <c r="J160" s="8" t="n"/>
-      <c r="K160" s="8" t="n"/>
-      <c r="L160" s="8" t="n"/>
-    </row>
-    <row r="161" ht="20" customHeight="1">
-      <c r="A161" s="8" t="n"/>
-      <c r="B161" s="8" t="n"/>
-      <c r="C161" s="8" t="n"/>
-      <c r="D161" s="8" t="n"/>
-      <c r="E161" s="8" t="n"/>
-      <c r="F161" s="8" t="n"/>
-      <c r="G161" s="8" t="n"/>
-      <c r="H161" s="8" t="n"/>
-      <c r="I161" s="8" t="n"/>
-      <c r="J161" s="8" t="n"/>
-      <c r="K161" s="8" t="n"/>
-      <c r="L161" s="8" t="n"/>
-    </row>
-    <row r="162" ht="8" customHeight="1"/>
-    <row r="163" ht="22" customHeight="1">
-      <c r="A163" s="31">
-        <f>"3-2. "&amp;(IF('예시-표지'!F7="","○○",'예시-표지'!F7))&amp;" 낙하물방지망 설치 도면"</f>
-        <v/>
-      </c>
-    </row>
-    <row r="164" ht="20" customHeight="1">
-      <c r="A164" s="32" t="inlineStr">
-        <is>
-          <t>(낙하물방지망 설치 도면 · 설치 사진을 붙이는 곳)</t>
-        </is>
-      </c>
-      <c r="B164" s="8" t="n"/>
-      <c r="C164" s="8" t="n"/>
-      <c r="D164" s="8" t="n"/>
-      <c r="E164" s="8" t="n"/>
-      <c r="F164" s="8" t="n"/>
-      <c r="G164" s="8" t="n"/>
-      <c r="H164" s="8" t="n"/>
-      <c r="I164" s="8" t="n"/>
-      <c r="J164" s="8" t="n"/>
-      <c r="K164" s="8" t="n"/>
-      <c r="L164" s="8" t="n"/>
-    </row>
-    <row r="165" ht="20" customHeight="1">
-      <c r="A165" s="8" t="n"/>
-      <c r="B165" s="8" t="n"/>
-      <c r="C165" s="8" t="n"/>
-      <c r="D165" s="8" t="n"/>
-      <c r="E165" s="8" t="n"/>
-      <c r="F165" s="8" t="n"/>
-      <c r="G165" s="8" t="n"/>
-      <c r="H165" s="8" t="n"/>
-      <c r="I165" s="8" t="n"/>
-      <c r="J165" s="8" t="n"/>
-      <c r="K165" s="8" t="n"/>
-      <c r="L165" s="8" t="n"/>
-    </row>
-    <row r="166" ht="20" customHeight="1">
-      <c r="A166" s="8" t="n"/>
-      <c r="B166" s="8" t="n"/>
-      <c r="C166" s="8" t="n"/>
-      <c r="D166" s="8" t="n"/>
-      <c r="E166" s="8" t="n"/>
-      <c r="F166" s="8" t="n"/>
-      <c r="G166" s="8" t="n"/>
-      <c r="H166" s="8" t="n"/>
-      <c r="I166" s="8" t="n"/>
-      <c r="J166" s="8" t="n"/>
-      <c r="K166" s="8" t="n"/>
-      <c r="L166" s="8" t="n"/>
-    </row>
-    <row r="167" ht="20" customHeight="1">
-      <c r="A167" s="8" t="n"/>
-      <c r="B167" s="8" t="n"/>
-      <c r="C167" s="8" t="n"/>
-      <c r="D167" s="8" t="n"/>
-      <c r="E167" s="8" t="n"/>
-      <c r="F167" s="8" t="n"/>
-      <c r="G167" s="8" t="n"/>
-      <c r="H167" s="8" t="n"/>
-      <c r="I167" s="8" t="n"/>
-      <c r="J167" s="8" t="n"/>
-      <c r="K167" s="8" t="n"/>
-      <c r="L167" s="8" t="n"/>
-    </row>
-    <row r="168" ht="20" customHeight="1">
-      <c r="A168" s="8" t="n"/>
-      <c r="B168" s="8" t="n"/>
-      <c r="C168" s="8" t="n"/>
-      <c r="D168" s="8" t="n"/>
-      <c r="E168" s="8" t="n"/>
-      <c r="F168" s="8" t="n"/>
-      <c r="G168" s="8" t="n"/>
-      <c r="H168" s="8" t="n"/>
-      <c r="I168" s="8" t="n"/>
-      <c r="J168" s="8" t="n"/>
-      <c r="K168" s="8" t="n"/>
-      <c r="L168" s="8" t="n"/>
-    </row>
-    <row r="169" ht="20" customHeight="1">
-      <c r="A169" s="8" t="n"/>
-      <c r="B169" s="8" t="n"/>
-      <c r="C169" s="8" t="n"/>
-      <c r="D169" s="8" t="n"/>
-      <c r="E169" s="8" t="n"/>
-      <c r="F169" s="8" t="n"/>
-      <c r="G169" s="8" t="n"/>
-      <c r="H169" s="8" t="n"/>
-      <c r="I169" s="8" t="n"/>
-      <c r="J169" s="8" t="n"/>
-      <c r="K169" s="8" t="n"/>
-      <c r="L169" s="8" t="n"/>
-    </row>
-    <row r="170" ht="20" customHeight="1">
-      <c r="A170" s="8" t="n"/>
-      <c r="B170" s="8" t="n"/>
-      <c r="C170" s="8" t="n"/>
-      <c r="D170" s="8" t="n"/>
-      <c r="E170" s="8" t="n"/>
-      <c r="F170" s="8" t="n"/>
-      <c r="G170" s="8" t="n"/>
-      <c r="H170" s="8" t="n"/>
-      <c r="I170" s="8" t="n"/>
-      <c r="J170" s="8" t="n"/>
-      <c r="K170" s="8" t="n"/>
-      <c r="L170" s="8" t="n"/>
-    </row>
-    <row r="171" ht="20" customHeight="1">
-      <c r="A171" s="8" t="n"/>
-      <c r="B171" s="8" t="n"/>
-      <c r="C171" s="8" t="n"/>
-      <c r="D171" s="8" t="n"/>
-      <c r="E171" s="8" t="n"/>
-      <c r="F171" s="8" t="n"/>
-      <c r="G171" s="8" t="n"/>
-      <c r="H171" s="8" t="n"/>
-      <c r="I171" s="8" t="n"/>
-      <c r="J171" s="8" t="n"/>
-      <c r="K171" s="8" t="n"/>
-      <c r="L171" s="8" t="n"/>
-    </row>
-    <row r="172" ht="20" customHeight="1">
-      <c r="A172" s="8" t="n"/>
-      <c r="B172" s="8" t="n"/>
-      <c r="C172" s="8" t="n"/>
-      <c r="D172" s="8" t="n"/>
-      <c r="E172" s="8" t="n"/>
-      <c r="F172" s="8" t="n"/>
-      <c r="G172" s="8" t="n"/>
-      <c r="H172" s="8" t="n"/>
-      <c r="I172" s="8" t="n"/>
-      <c r="J172" s="8" t="n"/>
-      <c r="K172" s="8" t="n"/>
-      <c r="L172" s="8" t="n"/>
-    </row>
-    <row r="173" ht="20" customHeight="1">
-      <c r="A173" s="8" t="n"/>
-      <c r="B173" s="8" t="n"/>
-      <c r="C173" s="8" t="n"/>
-      <c r="D173" s="8" t="n"/>
-      <c r="E173" s="8" t="n"/>
-      <c r="F173" s="8" t="n"/>
-      <c r="G173" s="8" t="n"/>
-      <c r="H173" s="8" t="n"/>
-      <c r="I173" s="8" t="n"/>
-      <c r="J173" s="8" t="n"/>
-      <c r="K173" s="8" t="n"/>
-      <c r="L173" s="8" t="n"/>
-    </row>
-    <row r="174" ht="20" customHeight="1">
-      <c r="A174" s="8" t="n"/>
-      <c r="B174" s="8" t="n"/>
-      <c r="C174" s="8" t="n"/>
-      <c r="D174" s="8" t="n"/>
-      <c r="E174" s="8" t="n"/>
-      <c r="F174" s="8" t="n"/>
-      <c r="G174" s="8" t="n"/>
-      <c r="H174" s="8" t="n"/>
-      <c r="I174" s="8" t="n"/>
-      <c r="J174" s="8" t="n"/>
-      <c r="K174" s="8" t="n"/>
-      <c r="L174" s="8" t="n"/>
-    </row>
-    <row r="175" ht="20" customHeight="1">
-      <c r="A175" s="8" t="n"/>
-      <c r="B175" s="8" t="n"/>
-      <c r="C175" s="8" t="n"/>
-      <c r="D175" s="8" t="n"/>
-      <c r="E175" s="8" t="n"/>
-      <c r="F175" s="8" t="n"/>
-      <c r="G175" s="8" t="n"/>
-      <c r="H175" s="8" t="n"/>
-      <c r="I175" s="8" t="n"/>
-      <c r="J175" s="8" t="n"/>
-      <c r="K175" s="8" t="n"/>
-      <c r="L175" s="8" t="n"/>
-    </row>
-    <row r="176" ht="20" customHeight="1">
-      <c r="A176" s="8" t="n"/>
-      <c r="B176" s="8" t="n"/>
-      <c r="C176" s="8" t="n"/>
-      <c r="D176" s="8" t="n"/>
-      <c r="E176" s="8" t="n"/>
-      <c r="F176" s="8" t="n"/>
-      <c r="G176" s="8" t="n"/>
-      <c r="H176" s="8" t="n"/>
-      <c r="I176" s="8" t="n"/>
-      <c r="J176" s="8" t="n"/>
-      <c r="K176" s="8" t="n"/>
-      <c r="L176" s="8" t="n"/>
-    </row>
-    <row r="177" ht="20" customHeight="1">
-      <c r="A177" s="8" t="n"/>
-      <c r="B177" s="8" t="n"/>
-      <c r="C177" s="8" t="n"/>
-      <c r="D177" s="8" t="n"/>
-      <c r="E177" s="8" t="n"/>
-      <c r="F177" s="8" t="n"/>
-      <c r="G177" s="8" t="n"/>
-      <c r="H177" s="8" t="n"/>
-      <c r="I177" s="8" t="n"/>
-      <c r="J177" s="8" t="n"/>
-      <c r="K177" s="8" t="n"/>
-      <c r="L177" s="8" t="n"/>
-    </row>
-    <row r="178" ht="4" customHeight="1"/>
-    <row r="179" ht="30" customHeight="1">
-      <c r="A179" s="18" t="inlineStr">
-        <is>
-          <t>4.  System Support 시공계획</t>
-        </is>
-      </c>
-    </row>
-    <row r="180" ht="4" customHeight="1"/>
-    <row r="181" ht="3" customHeight="1"/>
-    <row r="182" ht="22" customHeight="1">
-      <c r="A182" s="19" t="inlineStr">
-        <is>
-          <t>4-1. System Support 순서도</t>
-        </is>
-      </c>
-    </row>
-    <row r="183" ht="30" customHeight="1">
-      <c r="A183" s="5" t="inlineStr"/>
-      <c r="D183" s="34" t="inlineStr">
-        <is>
-          <t>도면 접수</t>
-        </is>
-      </c>
-      <c r="E183" s="8" t="n"/>
-      <c r="F183" s="8" t="n"/>
-      <c r="G183" s="8" t="n"/>
-      <c r="H183" s="8" t="n"/>
-      <c r="I183" s="8" t="n"/>
-      <c r="J183" s="35" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  ◀ 평면 · 단면 · 벽체 및 슬래브 등 치수</t>
-        </is>
-      </c>
-    </row>
-    <row r="184" ht="12" customHeight="1">
-      <c r="A184" s="36" t="inlineStr">
-        <is>
-          <t>▼</t>
-        </is>
-      </c>
-    </row>
-    <row r="185" ht="30" customHeight="1">
-      <c r="A185" s="5" t="inlineStr"/>
-      <c r="D185" s="34" t="inlineStr">
-        <is>
-          <t>구조 검토</t>
-        </is>
-      </c>
-      <c r="E185" s="8" t="n"/>
-      <c r="F185" s="8" t="n"/>
-      <c r="G185" s="8" t="n"/>
-      <c r="H185" s="8" t="n"/>
-      <c r="I185" s="8" t="n"/>
-      <c r="J185" s="35" t="inlineStr"/>
-    </row>
-    <row r="186" ht="12" customHeight="1">
-      <c r="A186" s="36" t="inlineStr">
-        <is>
-          <t>▼</t>
-        </is>
-      </c>
-    </row>
-    <row r="187" ht="30" customHeight="1">
-      <c r="A187" s="5" t="inlineStr"/>
-      <c r="D187" s="34" t="inlineStr">
-        <is>
-          <t>설치 설계</t>
-        </is>
-      </c>
-      <c r="E187" s="8" t="n"/>
-      <c r="F187" s="8" t="n"/>
-      <c r="G187" s="8" t="n"/>
-      <c r="H187" s="8" t="n"/>
-      <c r="I187" s="8" t="n"/>
-      <c r="J187" s="35" t="inlineStr"/>
-    </row>
-    <row r="188" ht="12" customHeight="1">
-      <c r="A188" s="36" t="inlineStr">
-        <is>
-          <t>▼</t>
-        </is>
-      </c>
-    </row>
-    <row r="189" ht="30" customHeight="1">
-      <c r="A189" s="5" t="inlineStr"/>
-      <c r="D189" s="34" t="inlineStr">
-        <is>
-          <t>검  토</t>
-        </is>
-      </c>
-      <c r="E189" s="8" t="n"/>
-      <c r="F189" s="8" t="n"/>
-      <c r="G189" s="8" t="n"/>
-      <c r="H189" s="8" t="n"/>
-      <c r="I189" s="8" t="n"/>
-      <c r="J189" s="35" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  ◀ 부적합 → 수정 후 다시 검토</t>
-        </is>
-      </c>
-    </row>
-    <row r="190" ht="12" customHeight="1">
-      <c r="A190" s="36" t="inlineStr">
-        <is>
-          <t>▼</t>
-        </is>
-      </c>
-    </row>
-    <row r="191" ht="30" customHeight="1">
-      <c r="A191" s="5" t="inlineStr"/>
-      <c r="D191" s="34" t="inlineStr">
-        <is>
-          <t>승  인</t>
-        </is>
-      </c>
-      <c r="E191" s="8" t="n"/>
-      <c r="F191" s="8" t="n"/>
-      <c r="G191" s="8" t="n"/>
-      <c r="H191" s="8" t="n"/>
-      <c r="I191" s="8" t="n"/>
-      <c r="J191" s="35" t="inlineStr"/>
-    </row>
-    <row r="192" ht="12" customHeight="1">
-      <c r="A192" s="36" t="inlineStr">
-        <is>
-          <t>▼</t>
-        </is>
-      </c>
-    </row>
-    <row r="193" ht="30" customHeight="1">
-      <c r="A193" s="5" t="inlineStr"/>
-      <c r="D193" s="34" t="inlineStr">
-        <is>
-          <t>동바리 설치</t>
-        </is>
-      </c>
-      <c r="E193" s="8" t="n"/>
-      <c r="F193" s="8" t="n"/>
-      <c r="G193" s="8" t="n"/>
-      <c r="H193" s="8" t="n"/>
-      <c r="I193" s="8" t="n"/>
-      <c r="J193" s="35" t="inlineStr"/>
-    </row>
-    <row r="194" ht="12" customHeight="1">
-      <c r="A194" s="36" t="inlineStr">
-        <is>
-          <t>▼</t>
-        </is>
-      </c>
-    </row>
-    <row r="195" ht="30" customHeight="1">
-      <c r="A195" s="5" t="inlineStr"/>
-      <c r="D195" s="34" t="inlineStr">
-        <is>
-          <t>구조물 작업 완료</t>
-        </is>
-      </c>
-      <c r="E195" s="8" t="n"/>
-      <c r="F195" s="8" t="n"/>
-      <c r="G195" s="8" t="n"/>
-      <c r="H195" s="8" t="n"/>
-      <c r="I195" s="8" t="n"/>
-      <c r="J195" s="35" t="inlineStr"/>
-    </row>
-    <row r="196" ht="12" customHeight="1">
-      <c r="A196" s="36" t="inlineStr">
-        <is>
-          <t>▼</t>
-        </is>
-      </c>
-    </row>
-    <row r="197" ht="30" customHeight="1">
-      <c r="A197" s="5" t="inlineStr"/>
-      <c r="D197" s="34" t="inlineStr">
-        <is>
-          <t>동바리 해체</t>
-        </is>
-      </c>
-      <c r="E197" s="8" t="n"/>
-      <c r="F197" s="8" t="n"/>
-      <c r="G197" s="8" t="n"/>
-      <c r="H197" s="8" t="n"/>
-      <c r="I197" s="8" t="n"/>
-      <c r="J197" s="35" t="inlineStr"/>
-    </row>
-    <row r="198" ht="3" customHeight="1"/>
-    <row r="199" ht="22" customHeight="1">
-      <c r="A199" s="19" t="inlineStr">
-        <is>
-          <t>4-2. System Support 조립 및 해체</t>
-        </is>
-      </c>
-    </row>
-    <row r="200" ht="21" customHeight="1">
-      <c r="A200" s="25" t="inlineStr">
-        <is>
-          <t>가. 조립 때 일반사항</t>
-        </is>
-      </c>
-    </row>
-    <row r="201" ht="37" customHeight="1">
-      <c r="A201" s="20" t="inlineStr">
-        <is>
-          <t>시스템 동바리는 연직하중을 지지하는 수직재, 상 · 하부 U헤드 잭과 잭 베이스, 수평력을 지지하는 수평재와 수직 · 수평가새로 이루어지며 다음에 맞아야 한다.</t>
-        </is>
-      </c>
-    </row>
-    <row r="202" ht="19.725" customHeight="1">
-      <c r="A202" s="26" t="inlineStr">
-        <is>
-          <t>(1)</t>
-        </is>
-      </c>
-      <c r="B202" s="27" t="inlineStr">
-        <is>
-          <t>구조설계에 따른 조립도대로 정확히 설치한다.</t>
-        </is>
-      </c>
-    </row>
-    <row r="203" ht="19.725" customHeight="1">
-      <c r="A203" s="26" t="inlineStr">
-        <is>
-          <t>(2)</t>
-        </is>
-      </c>
-      <c r="B203" s="27" t="inlineStr">
-        <is>
-          <t>수직재와 수평재는 직교가 되게 설치하며 체결 뒤 흔들림이 없어야 한다.</t>
-        </is>
-      </c>
-    </row>
-    <row r="204" ht="34.45" customHeight="1">
-      <c r="A204" s="26" t="inlineStr">
-        <is>
-          <t>(3)</t>
-        </is>
-      </c>
-      <c r="B204" s="27" t="inlineStr">
-        <is>
-          <t>설치 높이는 단변 길이의 3배를 넘지 않게 하며, 넘을 때는 주변 구조물에 지지하는 등 붕괴 방지 조치를 한다.</t>
-        </is>
-      </c>
-    </row>
-    <row r="205" ht="20" customHeight="1">
-      <c r="A205" s="37" t="inlineStr">
-        <is>
-          <t>(4) 잭 베이스의 전체 길이는 600mm 이내여야 하며, 수직재와 물림부의 겹침은 150mm 이상이어야 한다.</t>
-        </is>
-      </c>
-    </row>
-    <row r="206" ht="20" customHeight="1"/>
-    <row r="207" ht="20" customHeight="1"/>
-    <row r="208" ht="20" customHeight="1"/>
-    <row r="209" ht="20" customHeight="1"/>
-    <row r="210" ht="20" customHeight="1"/>
-    <row r="211" ht="20" customHeight="1"/>
-    <row r="212" ht="19.725" customHeight="1">
-      <c r="A212" s="26" t="inlineStr">
-        <is>
-          <t>(5)</t>
-        </is>
-      </c>
-      <c r="B212" s="27" t="inlineStr">
-        <is>
-          <t>수직재를 설치할 때는 수평재와 수직재 사이에 수직재 연결부가 2곳 이상 되지 않게 한다.</t>
-        </is>
-      </c>
-    </row>
-    <row r="213" ht="34.45" customHeight="1">
-      <c r="A213" s="26" t="inlineStr">
-        <is>
-          <t>(6)</t>
-        </is>
-      </c>
-      <c r="B213" s="27" t="inlineStr">
-        <is>
-          <t>처음 설치 때 잭 스크루를 조절하여 수평을 확보함으로써 수직재 편심에 의한 힘의 손실이 없게 한다.</t>
-        </is>
-      </c>
-    </row>
-    <row r="214" ht="19.725" customHeight="1">
-      <c r="A214" s="26" t="inlineStr">
-        <is>
-          <t>(7)</t>
-        </is>
-      </c>
-      <c r="B214" s="27" t="inlineStr">
-        <is>
-          <t>U헤드 잭에 얹히는 장선 · 멍에재는 편심이 생기지 않도록 중심선에 놓고 못 등으로 고정한다.</t>
-        </is>
-      </c>
-    </row>
-    <row r="215" ht="19.725" customHeight="1">
-      <c r="A215" s="26" t="inlineStr">
-        <is>
-          <t>(8)</t>
-        </is>
-      </c>
-      <c r="B215" s="27" t="inlineStr">
-        <is>
-          <t>최하부 수직재는 잭 베이스 너트와 밀착되게 설치한다.</t>
-        </is>
-      </c>
-    </row>
-    <row r="216" ht="20" customHeight="1">
-      <c r="A216" s="37" t="inlineStr">
-        <is>
-          <t>(9) 상부 U헤드 폭은 그림과 같이 멍에재 2개가 들어갈 수 있는 넓이 이상이어야 하며, 쐐기 등으로 멍에재와 U헤드를 밀착시켜 유격을 없앤다.
-(10) 연결핀으로 수직재를 단단히 조립하고 연결부가 꺾이지 않게 한다.</t>
-        </is>
-      </c>
-    </row>
-    <row r="217" ht="20" customHeight="1"/>
-    <row r="218" ht="20" customHeight="1"/>
-    <row r="219" ht="20" customHeight="1"/>
-    <row r="220" ht="20" customHeight="1"/>
-    <row r="221" ht="20" customHeight="1"/>
-    <row r="222" ht="20" customHeight="1"/>
-    <row r="223" ht="21" customHeight="1">
-      <c r="A223" s="25" t="inlineStr">
-        <is>
-          <t>나. 시스템 동바리의 조립 및 해체</t>
-        </is>
-      </c>
-    </row>
-    <row r="224" ht="21" customHeight="1">
-      <c r="A224" s="5" t="inlineStr"/>
-      <c r="B224" s="25" t="inlineStr">
-        <is>
-          <t>(1) 조립 전 점검 및 준비사항</t>
-        </is>
-      </c>
-    </row>
-    <row r="225" ht="34.45" customHeight="1">
-      <c r="A225" s="26" t="inlineStr">
-        <is>
-          <t>1)</t>
-        </is>
-      </c>
-      <c r="C225" s="27" t="inlineStr">
-        <is>
-          <t>지반에 설치할 때는 수직하중에 견디도록 지반 지지력을 검토하여 강재 · 목재 깔판 또는 깔목을 두거나, 지반 다짐 뒤 콘크리트를 타설하는 등 침하 방지 조치를 한다.</t>
-        </is>
-      </c>
-    </row>
-    <row r="226" ht="19.725" customHeight="1">
-      <c r="A226" s="26" t="inlineStr">
-        <is>
-          <t>2)</t>
-        </is>
-      </c>
-      <c r="C226" s="27" t="inlineStr">
-        <is>
-          <t>잭 베이스를 놓을 때는 밑에 이물질이나 돌출부가 없도록 바닥면을 정리한다.</t>
-        </is>
-      </c>
-    </row>
-    <row r="227" ht="19.725" customHeight="1">
-      <c r="A227" s="26" t="inlineStr">
-        <is>
-          <t>3)</t>
-        </is>
-      </c>
-      <c r="C227" s="27" t="inlineStr">
-        <is>
-          <t>바닥이 경사진 곳은 목재 쐐기 등으로 동바리 바닥이 수평이 되게 하고 서로 고정한다.</t>
-        </is>
-      </c>
-    </row>
-    <row r="228" ht="21" customHeight="1">
-      <c r="A228" s="5" t="inlineStr"/>
-      <c r="B228" s="25" t="inlineStr">
-        <is>
-          <t>(2) 조립 작업</t>
-        </is>
-      </c>
-    </row>
-    <row r="229" ht="20" customHeight="1">
-      <c r="A229" s="37" t="inlineStr">
-        <is>
-          <t>(가) 1단계
-작업 전 조립할 곳의 지반 상태와 작업원의 복장 · 개인보호구 · 건강 상태를 확인한다. 지반이 고르지 못하거나 지내력이 부족하면 담당자에게 알려 조치한 뒤 작업한다. 사전 조치가 끝나면 먹줄 매김 등으로 잭 베이스 위치를 표시하고, 잭 베이스에 하부 조절용 수직재를 끼워 설치 위치에 놓는다.</t>
-        </is>
-      </c>
-    </row>
-    <row r="230" ht="20" customHeight="1"/>
-    <row r="231" ht="20" customHeight="1"/>
-    <row r="232" ht="20" customHeight="1"/>
-    <row r="233" ht="20" customHeight="1"/>
-    <row r="234" ht="20" customHeight="1"/>
-    <row r="235" ht="20" customHeight="1"/>
-    <row r="236" ht="20" customHeight="1"/>
-    <row r="237" ht="20" customHeight="1"/>
-    <row r="238" ht="20" customHeight="1">
-      <c r="A238" s="37" t="inlineStr">
-        <is>
-          <t>(나) 2단계
-수직재에 수평재를 끼우고 핀을 살짝 끼운 뒤, 수평가새를 설치하여 위치를 고정한다.</t>
-        </is>
-      </c>
-    </row>
-    <row r="239" ht="20" customHeight="1"/>
-    <row r="240" ht="20" customHeight="1"/>
-    <row r="241" ht="20" customHeight="1"/>
-    <row r="242" ht="20" customHeight="1"/>
-    <row r="243" ht="20" customHeight="1"/>
-    <row r="244" ht="20" customHeight="1"/>
-    <row r="245" ht="20" customHeight="1"/>
-    <row r="246" ht="20" customHeight="1"/>
-    <row r="247" ht="20" customHeight="1">
-      <c r="A247" s="37" t="inlineStr">
-        <is>
-          <t>(다) 3단계
-수직재를 끼워 넣고, 이때 수직재의 대략적인 수평 · 수직 상태를 잡는다.</t>
-        </is>
-      </c>
-    </row>
-    <row r="248" ht="20" customHeight="1"/>
-    <row r="249" ht="20" customHeight="1"/>
-    <row r="250" ht="20" customHeight="1"/>
-    <row r="251" ht="20" customHeight="1"/>
-    <row r="252" ht="20" customHeight="1"/>
-    <row r="253" ht="20" customHeight="1"/>
-    <row r="254" ht="20" customHeight="1"/>
-    <row r="255" ht="20" customHeight="1"/>
-    <row r="256" ht="20" customHeight="1">
-      <c r="A256" s="37" t="inlineStr">
-        <is>
-          <t>(라) 4단계
-상부 수평재를 설치하고, 수직가새를 설치하며 수평을 맞춘 뒤 임시로 고정해 둔 연결핀을 완전히 고정한다. 연결핀에 유격이 있으면 동바리 전체가 흔들리므로 확실히 고정한다.</t>
-        </is>
-      </c>
-    </row>
-    <row r="257" ht="20" customHeight="1"/>
-    <row r="258" ht="20" customHeight="1"/>
-    <row r="259" ht="20" customHeight="1"/>
-    <row r="260" ht="20" customHeight="1"/>
-    <row r="261" ht="20" customHeight="1"/>
-    <row r="262" ht="20" customHeight="1"/>
-    <row r="263" ht="20" customHeight="1"/>
-    <row r="264" ht="20" customHeight="1"/>
-    <row r="265" ht="20" customHeight="1">
-      <c r="A265" s="37" t="inlineStr">
-        <is>
-          <t>(마) 5단계
-제품 사양에 맞는 작업발판을 쓰고, 2단으로 올라가기 전 안전대 착용 상태를 점검한다. 작업발판에 올라가 2단 수직재를 끼우고 수직가새를 설치한 뒤 연결핀을 완전히 고정하고 상부 수평재를 설치한다.</t>
-        </is>
-      </c>
-    </row>
-    <row r="266" ht="20" customHeight="1"/>
-    <row r="267" ht="20" customHeight="1"/>
-    <row r="268" ht="20" customHeight="1"/>
-    <row r="269" ht="20" customHeight="1"/>
-    <row r="270" ht="20" customHeight="1"/>
-    <row r="271" ht="20" customHeight="1"/>
-    <row r="272" ht="20" customHeight="1"/>
-    <row r="273" ht="20" customHeight="1"/>
-    <row r="274" ht="20" customHeight="1">
-      <c r="A274" s="37" t="inlineStr">
-        <is>
-          <t>(바) 6단계
-필요한 높이까지 같은 순서로 반복한다. 단 사이에는 제품 사양에 맞는 가설계단을 두고, 작업발판 높이가 2m 이상이면 안전대 부착설비(로프)를 먼저 설치한 뒤 안전대를 걸고 작업한다.</t>
-        </is>
-      </c>
-    </row>
-    <row r="275" ht="20" customHeight="1"/>
-    <row r="276" ht="20" customHeight="1"/>
-    <row r="277" ht="20" customHeight="1"/>
-    <row r="278" ht="20" customHeight="1"/>
-    <row r="279" ht="20" customHeight="1"/>
-    <row r="280" ht="20" customHeight="1"/>
-    <row r="281" ht="20" customHeight="1"/>
-    <row r="282" ht="20" customHeight="1"/>
-    <row r="283" ht="20" customHeight="1">
-      <c r="A283" s="37" t="inlineStr">
-        <is>
-          <t>(사) 7단계
-정해진 높이까지 설치가 끝나면 최상단에 멍에재 설치 및 높이 조절을 위한 U헤드 잭을 달아 조절하고, 조립 부분 전체 상태를 점검한다.</t>
-        </is>
-      </c>
-    </row>
-    <row r="284" ht="20" customHeight="1"/>
-    <row r="285" ht="20" customHeight="1"/>
-    <row r="286" ht="20" customHeight="1"/>
-    <row r="287" ht="20" customHeight="1"/>
-    <row r="288" ht="20" customHeight="1"/>
-    <row r="289" ht="20" customHeight="1"/>
-    <row r="290" ht="20" customHeight="1"/>
-    <row r="291" ht="20" customHeight="1"/>
-    <row r="292" ht="21" customHeight="1">
-      <c r="A292" s="5" t="inlineStr"/>
-      <c r="B292" s="25" t="inlineStr">
-        <is>
-          <t>(3) 해체 작업</t>
-        </is>
-      </c>
-    </row>
-    <row r="293" ht="34.45" customHeight="1">
-      <c r="A293" s="26" t="inlineStr">
-        <is>
-          <t>(가)</t>
-        </is>
-      </c>
-      <c r="C293" s="27" t="inlineStr">
-        <is>
-          <t>해체는 조립의 역순으로 하며, 작업 전 해체계획을 세우고 작업지휘자의 지시에 따라 한다.</t>
-        </is>
-      </c>
-    </row>
-    <row r="294" ht="34.45" customHeight="1">
-      <c r="A294" s="26" t="inlineStr">
-        <is>
-          <t>(나)</t>
-        </is>
-      </c>
-      <c r="C294" s="27" t="inlineStr">
-        <is>
-          <t>해체한 자재는 규격별로 정리하고, 운반할 때도 같은 규격끼리 묶어 옮기며 부재가 변형되지 않게 주의한다.</t>
-        </is>
-      </c>
-    </row>
-    <row r="295" ht="21" customHeight="1">
-      <c r="A295" s="5" t="inlineStr"/>
-      <c r="B295" s="25" t="inlineStr">
-        <is>
-          <t>(4) 해체 작업 때 안전조치</t>
-        </is>
-      </c>
-    </row>
-    <row r="296" ht="34.45" customHeight="1">
-      <c r="A296" s="26" t="inlineStr">
-        <is>
-          <t>(가)</t>
-        </is>
-      </c>
-      <c r="C296" s="27" t="inlineStr">
-        <is>
-          <t>조립 작업 때 작업발판 사이에는 근로자가 안전하게 다닐 수 있도록 가설계단 등을 설치한다.</t>
-        </is>
-      </c>
-    </row>
-    <row r="297" ht="19.725" customHeight="1">
-      <c r="A297" s="26" t="inlineStr">
-        <is>
-          <t>(나)</t>
-        </is>
-      </c>
-      <c r="C297" s="27" t="inlineStr">
-        <is>
-          <t>해체한 자재를 던지지 않는다.</t>
-        </is>
-      </c>
-    </row>
-    <row r="298" ht="19.725" customHeight="1">
-      <c r="A298" s="26" t="inlineStr">
-        <is>
-          <t>(다)</t>
-        </is>
-      </c>
-      <c r="C298" s="27" t="inlineStr">
-        <is>
-          <t>작업 장소에 출입금지구역을 정해 작업자 외의 출입을 막고 감시인을 둔다.</t>
-        </is>
-      </c>
-    </row>
-    <row r="299" ht="19.725" customHeight="1">
-      <c r="A299" s="26" t="inlineStr">
-        <is>
-          <t>(라)</t>
-        </is>
-      </c>
-      <c r="C299" s="27" t="inlineStr">
-        <is>
-          <t>조립 · 해체 작업자에게 작업 전에 교육을 한다.</t>
-        </is>
-      </c>
-    </row>
-    <row r="300" ht="19.725" customHeight="1">
-      <c r="A300" s="26" t="inlineStr">
-        <is>
-          <t>(마)</t>
-        </is>
-      </c>
-      <c r="C300" s="27" t="inlineStr">
-        <is>
-          <t>작업에 맞는 개인보호구(안전모 · 안전대 · 안전화 · 안전장갑 등)를 착용한다.</t>
-        </is>
-      </c>
-    </row>
-    <row r="302" ht="19.5" customHeight="1">
-      <c r="A302" s="15" t="inlineStr">
-        <is>
-          <t>이 시트는 작성 예시입니다.</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="199">
-    <mergeCell ref="A193:C193"/>
-    <mergeCell ref="B91:L91"/>
-    <mergeCell ref="A64:B64"/>
-    <mergeCell ref="A80:C80"/>
-    <mergeCell ref="A73:B73"/>
-    <mergeCell ref="D185:I185"/>
-    <mergeCell ref="D81:H81"/>
-    <mergeCell ref="A226:B226"/>
-    <mergeCell ref="C299:L299"/>
-    <mergeCell ref="J197:L197"/>
-    <mergeCell ref="A70:B70"/>
-    <mergeCell ref="B93:L93"/>
-    <mergeCell ref="A192:L192"/>
-    <mergeCell ref="A145:L145"/>
-    <mergeCell ref="J187:L187"/>
-    <mergeCell ref="B215:L215"/>
-    <mergeCell ref="A179:L179"/>
-    <mergeCell ref="A185:C185"/>
-    <mergeCell ref="C293:L293"/>
-    <mergeCell ref="A7:B7"/>
-    <mergeCell ref="J183:L183"/>
-    <mergeCell ref="A129:L129"/>
-    <mergeCell ref="A283:F291"/>
-    <mergeCell ref="A302:L302"/>
-    <mergeCell ref="B39:L39"/>
-    <mergeCell ref="A32:F32"/>
-    <mergeCell ref="A194:L194"/>
-    <mergeCell ref="I81:L81"/>
-    <mergeCell ref="D183:I183"/>
-    <mergeCell ref="A74:B74"/>
-    <mergeCell ref="A184:L184"/>
-    <mergeCell ref="C74:L74"/>
-    <mergeCell ref="A294:B294"/>
-    <mergeCell ref="G32:L32"/>
-    <mergeCell ref="B38:L38"/>
-    <mergeCell ref="A76:B76"/>
-    <mergeCell ref="C11:J11"/>
-    <mergeCell ref="B87:L87"/>
-    <mergeCell ref="A83:C83"/>
-    <mergeCell ref="B40:L40"/>
-    <mergeCell ref="D187:I187"/>
-    <mergeCell ref="A148:F161"/>
-    <mergeCell ref="C75:L75"/>
-    <mergeCell ref="A68:B68"/>
-    <mergeCell ref="C13:J13"/>
-    <mergeCell ref="A9:B9"/>
-    <mergeCell ref="K13:L13"/>
-    <mergeCell ref="B41:L41"/>
-    <mergeCell ref="B212:L212"/>
-    <mergeCell ref="A196:L196"/>
-    <mergeCell ref="A78:L78"/>
-    <mergeCell ref="A183:C183"/>
-    <mergeCell ref="I83:L83"/>
-    <mergeCell ref="C70:L70"/>
-    <mergeCell ref="A11:B11"/>
-    <mergeCell ref="B90:L90"/>
-    <mergeCell ref="A225:B225"/>
-    <mergeCell ref="D80:H80"/>
-    <mergeCell ref="A296:B296"/>
-    <mergeCell ref="C296:L296"/>
-    <mergeCell ref="A3:L3"/>
-    <mergeCell ref="A33:F33"/>
-    <mergeCell ref="I84:L84"/>
-    <mergeCell ref="A227:B227"/>
-    <mergeCell ref="C298:L298"/>
-    <mergeCell ref="C10:J10"/>
-    <mergeCell ref="D193:I193"/>
-    <mergeCell ref="A79:L79"/>
-    <mergeCell ref="A97:L97"/>
-    <mergeCell ref="A216:H222"/>
-    <mergeCell ref="I80:L80"/>
-    <mergeCell ref="A81:C81"/>
-    <mergeCell ref="A200:L200"/>
-    <mergeCell ref="C9:J9"/>
-    <mergeCell ref="A147:L147"/>
-    <mergeCell ref="C73:L73"/>
-    <mergeCell ref="A298:B298"/>
-    <mergeCell ref="B37:L37"/>
-    <mergeCell ref="C63:L63"/>
-    <mergeCell ref="A8:B8"/>
-    <mergeCell ref="A186:L186"/>
-    <mergeCell ref="A82:C82"/>
-    <mergeCell ref="A201:L201"/>
-    <mergeCell ref="D83:H83"/>
-    <mergeCell ref="A63:B63"/>
-    <mergeCell ref="A299:B299"/>
-    <mergeCell ref="A10:B10"/>
-    <mergeCell ref="K10:L10"/>
-    <mergeCell ref="A197:C197"/>
-    <mergeCell ref="B95:L95"/>
-    <mergeCell ref="A293:B293"/>
-    <mergeCell ref="B89:L89"/>
-    <mergeCell ref="K6:L6"/>
-    <mergeCell ref="D85:H85"/>
-    <mergeCell ref="A100:L112"/>
-    <mergeCell ref="A187:C187"/>
-    <mergeCell ref="C300:L300"/>
-    <mergeCell ref="D195:I195"/>
-    <mergeCell ref="D189:I189"/>
-    <mergeCell ref="B224:L224"/>
-    <mergeCell ref="A84:C84"/>
-    <mergeCell ref="I82:L82"/>
-    <mergeCell ref="B203:L203"/>
-    <mergeCell ref="C6:J6"/>
-    <mergeCell ref="A229:F237"/>
-    <mergeCell ref="K9:L9"/>
-    <mergeCell ref="A189:C189"/>
-    <mergeCell ref="K5:L5"/>
-    <mergeCell ref="D197:I197"/>
-    <mergeCell ref="C297:L297"/>
-    <mergeCell ref="C67:L67"/>
-    <mergeCell ref="A18:L18"/>
-    <mergeCell ref="B292:L292"/>
-    <mergeCell ref="A300:B300"/>
-    <mergeCell ref="A223:L223"/>
-    <mergeCell ref="C72:L72"/>
-    <mergeCell ref="A69:B69"/>
-    <mergeCell ref="B71:L71"/>
-    <mergeCell ref="A256:F264"/>
-    <mergeCell ref="G33:L33"/>
-    <mergeCell ref="B43:L43"/>
-    <mergeCell ref="K11:L11"/>
-    <mergeCell ref="A86:L86"/>
-    <mergeCell ref="B214:L214"/>
-    <mergeCell ref="B228:L228"/>
-    <mergeCell ref="A65:B65"/>
-    <mergeCell ref="C69:L69"/>
-    <mergeCell ref="A75:B75"/>
-    <mergeCell ref="B42:L42"/>
-    <mergeCell ref="A12:B12"/>
-    <mergeCell ref="C225:L225"/>
-    <mergeCell ref="A199:L199"/>
-    <mergeCell ref="B44:L44"/>
-    <mergeCell ref="K8:L8"/>
-    <mergeCell ref="J189:L189"/>
-    <mergeCell ref="A238:F246"/>
-    <mergeCell ref="A297:B297"/>
-    <mergeCell ref="C64:L64"/>
-    <mergeCell ref="A247:F255"/>
-    <mergeCell ref="A5:B5"/>
-    <mergeCell ref="C227:L227"/>
-    <mergeCell ref="A114:L114"/>
-    <mergeCell ref="C8:J8"/>
-    <mergeCell ref="A59:L59"/>
-    <mergeCell ref="A191:C191"/>
-    <mergeCell ref="K7:L7"/>
-    <mergeCell ref="A15:L15"/>
-    <mergeCell ref="C226:L226"/>
-    <mergeCell ref="B92:L92"/>
-    <mergeCell ref="A1:F1"/>
-    <mergeCell ref="D82:H82"/>
-    <mergeCell ref="A61:L61"/>
-    <mergeCell ref="B204:L204"/>
-    <mergeCell ref="B213:L213"/>
-    <mergeCell ref="A67:B67"/>
-    <mergeCell ref="B94:L94"/>
-    <mergeCell ref="A274:F282"/>
-    <mergeCell ref="C76:L76"/>
-    <mergeCell ref="B62:L62"/>
-    <mergeCell ref="A99:L99"/>
-    <mergeCell ref="A115:L127"/>
-    <mergeCell ref="B202:L202"/>
-    <mergeCell ref="B295:L295"/>
-    <mergeCell ref="C5:J5"/>
-    <mergeCell ref="D84:H84"/>
-    <mergeCell ref="J191:L191"/>
-    <mergeCell ref="A6:B6"/>
-    <mergeCell ref="A130:L142"/>
-    <mergeCell ref="C66:L66"/>
-    <mergeCell ref="A163:L163"/>
-    <mergeCell ref="A195:C195"/>
-    <mergeCell ref="A164:L177"/>
-    <mergeCell ref="A85:C85"/>
-    <mergeCell ref="G148:L161"/>
-    <mergeCell ref="J193:L193"/>
-    <mergeCell ref="C68:L68"/>
-    <mergeCell ref="A66:B66"/>
-    <mergeCell ref="A188:L188"/>
-    <mergeCell ref="A35:L35"/>
-    <mergeCell ref="C294:L294"/>
-    <mergeCell ref="G1:L1"/>
-    <mergeCell ref="C12:J12"/>
-    <mergeCell ref="B88:L88"/>
-    <mergeCell ref="K12:L12"/>
-    <mergeCell ref="A19:L19"/>
-    <mergeCell ref="A190:L190"/>
-    <mergeCell ref="J185:L185"/>
-    <mergeCell ref="I85:L85"/>
-    <mergeCell ref="C65:L65"/>
-    <mergeCell ref="D191:I191"/>
-    <mergeCell ref="A205:H211"/>
-    <mergeCell ref="A72:B72"/>
-    <mergeCell ref="C7:J7"/>
-    <mergeCell ref="A265:F273"/>
-    <mergeCell ref="A182:L182"/>
-    <mergeCell ref="A13:B13"/>
-    <mergeCell ref="B36:L36"/>
-    <mergeCell ref="B45:L45"/>
-    <mergeCell ref="J195:L195"/>
-  </mergeCells>
-  <printOptions horizontalCentered="1"/>
-  <pageMargins left="0.6" right="0.6" top="0.6" bottom="0.6" header="0.2" footer="0.2"/>
-  <pageSetup orientation="portrait" paperSize="9" fitToHeight="0" fitToWidth="1"/>
-  <rowBreaks count="10" manualBreakCount="10">
-    <brk id="13" min="0" max="16383" man="1"/>
-    <brk id="45" min="0" max="16383" man="1"/>
-    <brk id="76" min="0" max="16383" man="1"/>
-    <brk id="95" min="0" max="16383" man="1"/>
-    <brk id="128" min="0" max="16383" man="1"/>
-    <brk id="143" min="0" max="16383" man="1"/>
-    <brk id="177" min="0" max="16383" man="1"/>
-    <brk id="213" min="0" max="16383" man="1"/>
-    <brk id="246" min="0" max="16383" man="1"/>
-    <brk id="282" min="0" max="16383" man="1"/>
-  </rowBreaks>
-  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <tabColor rgb="00F59E0B"/>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr fitToPage="1"/>
-  </sheetPr>
-  <dimension ref="A1:L15"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="7.6" customWidth="1" min="1" max="1"/>
-    <col width="7.6" customWidth="1" min="2" max="2"/>
-    <col width="7.6" customWidth="1" min="3" max="3"/>
-    <col width="7.6" customWidth="1" min="4" max="4"/>
-    <col width="7.6" customWidth="1" min="5" max="5"/>
-    <col width="7.6" customWidth="1" min="6" max="6"/>
-    <col width="7.6" customWidth="1" min="7" max="7"/>
-    <col width="7.6" customWidth="1" min="8" max="8"/>
-    <col width="7.6" customWidth="1" min="9" max="9"/>
-    <col width="7.6" customWidth="1" min="10" max="10"/>
-    <col width="7.6" customWidth="1" min="11" max="11"/>
-    <col width="7.6" customWidth="1" min="12" max="12"/>
-  </cols>
-  <sheetData>
-    <row r="1" ht="20" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  K-건설맵  |  k-conmap.com  건설 서식</t>
-        </is>
-      </c>
-      <c r="G1" s="51" t="inlineStr">
-        <is>
-          <t xml:space="preserve">작성 예시 (가상의 현장)  </t>
-        </is>
-      </c>
-    </row>
-    <row r="2" ht="40" customHeight="1">
-      <c r="A2" s="38" t="inlineStr">
-        <is>
-          <t>시스템 동바리  설치 조건 확인표</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="26" customHeight="1">
-      <c r="A3" s="7" t="inlineStr">
-        <is>
-          <t>대상 구조물</t>
-        </is>
-      </c>
-      <c r="B3" s="8" t="n"/>
-      <c r="C3" s="8" t="n"/>
-      <c r="D3" s="39">
-        <f>IF('예시-표지'!F7="","",'예시-표지'!F7)</f>
-        <v/>
-      </c>
-      <c r="E3" s="8" t="n"/>
-      <c r="F3" s="8" t="n"/>
-      <c r="G3" s="8" t="n"/>
-      <c r="H3" s="7" t="inlineStr">
-        <is>
-          <t>확 인 일</t>
-        </is>
-      </c>
-      <c r="I3" s="8" t="n"/>
-      <c r="J3" s="40" t="n">
-        <v>46307</v>
-      </c>
-      <c r="K3" s="8" t="n"/>
-      <c r="L3" s="8" t="n"/>
-    </row>
-    <row r="4" ht="24" customHeight="1">
-      <c r="A4" s="28" t="inlineStr">
-        <is>
-          <t>확 인 항 목</t>
-        </is>
-      </c>
-      <c r="B4" s="8" t="n"/>
-      <c r="C4" s="8" t="n"/>
-      <c r="D4" s="28" t="inlineStr">
-        <is>
-          <t>값</t>
-        </is>
-      </c>
-      <c r="E4" s="8" t="n"/>
-      <c r="F4" s="28" t="inlineStr">
-        <is>
-          <t>기  준</t>
-        </is>
-      </c>
-      <c r="G4" s="8" t="n"/>
-      <c r="H4" s="8" t="n"/>
-      <c r="I4" s="28" t="inlineStr">
-        <is>
-          <t>비  교</t>
-        </is>
-      </c>
-      <c r="J4" s="8" t="n"/>
-      <c r="K4" s="28" t="inlineStr">
-        <is>
-          <t>판  정</t>
-        </is>
-      </c>
-      <c r="L4" s="8" t="n"/>
-    </row>
-    <row r="5" ht="24" customHeight="1">
-      <c r="A5" s="7" t="inlineStr">
-        <is>
-          <t>설치 높이 H</t>
-        </is>
-      </c>
-      <c r="B5" s="8" t="n"/>
-      <c r="C5" s="8" t="n"/>
-      <c r="D5" s="41" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="E5" s="8" t="n"/>
-      <c r="F5" s="42" t="inlineStr">
-        <is>
-          <t>H ≤ 3 × 단변 길이 B</t>
-        </is>
-      </c>
-      <c r="G5" s="8" t="n"/>
-      <c r="H5" s="8" t="n"/>
-      <c r="I5" s="43">
-        <f>IF(OR(N(D5)=0,N(D6)=0),"",ROUND(D5/D6,2))</f>
-        <v/>
-      </c>
-      <c r="J5" s="8" t="n"/>
-      <c r="K5" s="44">
-        <f>IF(I5="","",IF(I5&lt;=3,"적합","부적합 — 붕괴방지 조치"))</f>
-        <v/>
-      </c>
-      <c r="L5" s="8" t="n"/>
-    </row>
-    <row r="6" ht="24" customHeight="1">
-      <c r="A6" s="7" t="inlineStr">
-        <is>
-          <t>단변 길이 B</t>
-        </is>
-      </c>
-      <c r="B6" s="8" t="n"/>
-      <c r="C6" s="8" t="n"/>
-      <c r="D6" s="41" t="n">
-        <v>6</v>
-      </c>
-      <c r="E6" s="8" t="n"/>
-      <c r="F6" s="8" t="n"/>
-      <c r="G6" s="8" t="n"/>
-      <c r="H6" s="8" t="n"/>
-      <c r="I6" s="8" t="n"/>
-      <c r="J6" s="8" t="n"/>
-      <c r="K6" s="8" t="n"/>
-      <c r="L6" s="8" t="n"/>
-    </row>
-    <row r="7" ht="24" customHeight="1">
-      <c r="A7" s="7" t="inlineStr">
-        <is>
-          <t>잭 베이스 전체 길이</t>
-        </is>
-      </c>
-      <c r="B7" s="8" t="n"/>
-      <c r="C7" s="8" t="n"/>
-      <c r="D7" s="45" t="n">
-        <v>450</v>
-      </c>
-      <c r="E7" s="8" t="n"/>
-      <c r="F7" s="42" t="inlineStr">
-        <is>
-          <t>600mm 이내</t>
-        </is>
-      </c>
-      <c r="G7" s="8" t="n"/>
-      <c r="H7" s="8" t="n"/>
-      <c r="I7" s="46" t="inlineStr"/>
-      <c r="J7" s="8" t="n"/>
-      <c r="K7" s="44">
-        <f>IF(N(D7)=0,"",IF(D7&lt;=600,"적합","부적합"))</f>
-        <v/>
-      </c>
-      <c r="L7" s="8" t="n"/>
-    </row>
-    <row r="8" ht="24" customHeight="1">
-      <c r="A8" s="7" t="inlineStr">
-        <is>
-          <t>수직재 물림부 겹침</t>
-        </is>
-      </c>
-      <c r="B8" s="8" t="n"/>
-      <c r="C8" s="8" t="n"/>
-      <c r="D8" s="45" t="n">
-        <v>200</v>
-      </c>
-      <c r="E8" s="8" t="n"/>
-      <c r="F8" s="42" t="inlineStr">
-        <is>
-          <t>150mm 이상</t>
-        </is>
-      </c>
-      <c r="G8" s="8" t="n"/>
-      <c r="H8" s="8" t="n"/>
-      <c r="I8" s="46" t="inlineStr"/>
-      <c r="J8" s="8" t="n"/>
-      <c r="K8" s="44">
-        <f>IF(N(D8)=0,"",IF(D8&gt;=150,"적합","부적합"))</f>
-        <v/>
-      </c>
-      <c r="L8" s="8" t="n"/>
-    </row>
-    <row r="9" ht="24" customHeight="1">
-      <c r="A9" s="7" t="inlineStr">
-        <is>
-          <t>U헤드 안쪽 폭 (mm)</t>
-        </is>
-      </c>
-      <c r="B9" s="8" t="n"/>
-      <c r="C9" s="8" t="n"/>
-      <c r="D9" s="47" t="n">
-        <v>210</v>
-      </c>
-      <c r="E9" s="8" t="n"/>
-      <c r="F9" s="42" t="inlineStr">
-        <is>
-          <t>U헤드 폭 ≥ 멍에재 2개 폭</t>
-        </is>
-      </c>
-      <c r="G9" s="8" t="n"/>
-      <c r="H9" s="8" t="n"/>
-      <c r="I9" s="48">
-        <f>IF(OR(N(D9)=0,N(D10)=0),"",D9-2*D10)</f>
-        <v/>
-      </c>
-      <c r="J9" s="8" t="n"/>
-      <c r="K9" s="44">
-        <f>IF(I9="","",IF(I9&gt;=0,"적합","부적합"))</f>
-        <v/>
-      </c>
-      <c r="L9" s="8" t="n"/>
-    </row>
-    <row r="10" ht="24" customHeight="1">
-      <c r="A10" s="7" t="inlineStr">
-        <is>
-          <t>멍에재 폭 1개 (mm)</t>
-        </is>
-      </c>
-      <c r="B10" s="8" t="n"/>
-      <c r="C10" s="8" t="n"/>
-      <c r="D10" s="47" t="n">
-        <v>100</v>
-      </c>
-      <c r="E10" s="8" t="n"/>
-      <c r="F10" s="8" t="n"/>
-      <c r="G10" s="8" t="n"/>
-      <c r="H10" s="8" t="n"/>
-      <c r="I10" s="8" t="n"/>
-      <c r="J10" s="8" t="n"/>
-      <c r="K10" s="8" t="n"/>
-      <c r="L10" s="8" t="n"/>
-    </row>
-    <row r="11" ht="28" customHeight="1">
-      <c r="A11" s="49" t="inlineStr">
-        <is>
-          <t>종 합</t>
-        </is>
-      </c>
-      <c r="B11" s="8" t="n"/>
-      <c r="C11" s="8" t="n"/>
-      <c r="D11" s="50">
-        <f>IF((K5&amp;K7&amp;K8&amp;K9)="","",IF(COUNTIF(K5,"부*")+COUNTIF(K7,"부*")+COUNTIF(K8,"부*")+COUNTIF(K9,"부*")=0,IF(AND(K5&lt;&gt;"",K7&lt;&gt;"",K8&lt;&gt;"",K9&lt;&gt;""),"모두 적합","적합(빈 항목 있음)"),"⚠ 부적합 항목 — 설치 계획 · 구조검토 다시 확인"))</f>
-        <v/>
-      </c>
-      <c r="E11" s="8" t="n"/>
-      <c r="F11" s="8" t="n"/>
-      <c r="G11" s="8" t="n"/>
-      <c r="H11" s="8" t="n"/>
-      <c r="I11" s="8" t="n"/>
-      <c r="J11" s="8" t="n"/>
-      <c r="K11" s="8" t="n"/>
-      <c r="L11" s="8" t="n"/>
-    </row>
-    <row r="12" ht="34" customHeight="1">
-      <c r="A12" s="7" t="inlineStr">
-        <is>
-          <t>확 인 자</t>
-        </is>
-      </c>
-      <c r="B12" s="8" t="n"/>
-      <c r="C12" s="8" t="n"/>
-      <c r="D12" s="9" t="inlineStr">
-        <is>
-          <t>홍길동</t>
-        </is>
-      </c>
-      <c r="E12" s="8" t="n"/>
-      <c r="F12" s="8" t="n"/>
-      <c r="G12" s="7" t="inlineStr">
-        <is>
-          <t>서    명</t>
-        </is>
-      </c>
-      <c r="H12" s="8" t="n"/>
-      <c r="I12" s="8" t="n"/>
-      <c r="J12" s="46" t="inlineStr"/>
-      <c r="K12" s="8" t="n"/>
-      <c r="L12" s="8" t="n"/>
-    </row>
-    <row r="13" ht="29.65" customHeight="1">
-      <c r="A13" s="30" t="inlineStr">
-        <is>
-          <t>※ 기준은 이 계획서 «4-2 가. 조립 때 일반사항» 의 값입니다. 멍에재 폭 · U헤드 폭은 mm 로 적습니다. 구조검토서 · 제조사 조립 기준이 따로 있으면 그것을 따릅니다.</t>
-        </is>
-      </c>
-    </row>
-    <row r="15" ht="19.5" customHeight="1">
-      <c r="A15" s="15" t="inlineStr">
-        <is>
-          <t>이 시트는 작성 예시입니다(가상의 값).</t>
         </is>
       </c>
     </row>

--- a/web/public/forms/orig/o-dongbari-gyehoekseo.xlsx
+++ b/web/public/forms/orig/o-dongbari-gyehoekseo.xlsx
@@ -1062,7 +1062,7 @@
     <row r="1" ht="20" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">  K-건설맵  |  k-conmap.com  건설 서식</t>
+          <t xml:space="preserve">  K-건설맵  |  k-conmap.com  무료 건설 서식</t>
         </is>
       </c>
       <c r="G1" s="2" t="inlineStr">
@@ -1221,7 +1221,7 @@
     <row r="1" ht="20" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">  K-건설맵  |  k-conmap.com  건설 서식</t>
+          <t xml:space="preserve">  K-건설맵  |  k-conmap.com  무료 건설 서식</t>
         </is>
       </c>
       <c r="G1" s="2" t="inlineStr">
@@ -3822,7 +3822,7 @@
     <row r="1" ht="20" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">  K-건설맵  |  k-conmap.com  건설 서식</t>
+          <t xml:space="preserve">  K-건설맵  |  k-conmap.com  무료 건설 서식</t>
         </is>
       </c>
       <c r="G1" s="2" t="inlineStr">
